--- a/antares/twin/docs/Кошторис_будівництва_під_ключ_СЕС_АБК_Антарес_ДБН_інвертор_Deye_100_кВт_28.10.2026.xlsx
+++ b/antares/twin/docs/Кошторис_будівництва_під_ключ_СЕС_АБК_Антарес_ДБН_інвертор_Deye_100_кВт_28.10.2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="699">
   <si>
     <t xml:space="preserve">Кошторис будівництва під ключ — СЕС на даху АБК, ТОВ МК «Антарес», варіант «ДБН»</t>
   </si>
@@ -85,10 +85,10 @@
     <t xml:space="preserve">1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Кріплення на арці по даху: лаги, гільзи, шпильки, профілі, кутники, притиски, метизи</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arch roof mounting: rails, sleeves, rods, profiles, angles, clamps, fasteners</t>
+    <t xml:space="preserve">Кріплення на арці «Лага 0°»: лаги 41×41, гільзи з муфтами, шпильки M10, крайні профілі, кутники, притиски, метизи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arch mounting "Rail 0°": 41×41 rails, sleeves with couplings, M10 rods, edge profiles, angles, clamps, fasteners</t>
   </si>
   <si>
     <t xml:space="preserve">модуль / module</t>
@@ -100,10 +100,10 @@
     <t xml:space="preserve">1.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Кріплення «домік» 15° на нижньому даху і надбудові: трикутники, кронштейни, притиски, метизи</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dual-tilt 15° mounting on lower roof and stair house: triangles, brackets, clamps, fasteners</t>
+    <t xml:space="preserve">Кріплення 15° на нижньому даху і надбудові: опори «доміку» і трикутники під одиночні модулі, П-кронштейни, діагоналі, притиски, метизи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15° mounting on lower roof and stair house: dual-tilt supports and triangles for single modules, U-brackets, diagonals, clamps, fasteners</t>
   </si>
   <si>
     <t xml:space="preserve">ГалКат 15° 22.10, на модуль / per module</t>
@@ -112,10 +112,10 @@
     <t xml:space="preserve">1.4</t>
   </si>
   <si>
-    <t xml:space="preserve">Кріплення на південних стінах: рейки, кронштейни з анкерами, притиски</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South wall mounting: rails, brackets with anchors, clamps</t>
+    <t xml:space="preserve">Кріплення на південних стінах: рейки 41×41×2,5, кронштейни з анкерами, притиски, трос безпеки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South wall mounting: 41×41×2.5 rails, brackets with anchors, clamps, safety rope</t>
   </si>
   <si>
     <t xml:space="preserve">кошторис під ключ 27.10 / turnkey estimate 27.10, поз. 1.3.2</t>
@@ -286,10 +286,10 @@
     <t xml:space="preserve">4.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Баластний блок 300×300×60 з муфтою і матом — арка, «домік», опори лотків (+1 %)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ballast block 300×300×60 with coupling and mat — arch, dual-tilt, tray supports (+1 %)</t>
+    <t xml:space="preserve">Баластний блок 300×300×60 з муфтою: під лаги, опори «доміку» і трикутники — з матом, під крайні профілі арки — без мата; опори лотків (+1 %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ballast block 300×300×60 with coupling: under rails, dual-tilt supports and triangles — with mat, under arch edge profiles — without mat; tray supports (+1 %)</t>
   </si>
   <si>
     <t xml:space="preserve">рішення власника 26.10 / owner decision</t>
@@ -421,6 +421,18 @@
     <t xml:space="preserve">reziplit.in.ua, 28.10.2026</t>
   </si>
   <si>
+    <t xml:space="preserve">4.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Анкер від сповзання на арці, до основи покрівлі, з герметизацією</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anti-slide anchor on the arch, to the roof deck, with sealing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">кошторис СЕС і УЗЕ 26.10 / estimate 26.10</t>
+  </si>
+  <si>
     <t xml:space="preserve">Разом купуємо в Україні</t>
   </si>
   <si>
@@ -694,202 +706,439 @@
     <t xml:space="preserve">132 у стрінгах (арка 86, нижній дах 31, надбудова 6, стіни 9) + 2 % / 132 in strings + 2 %</t>
   </si>
   <si>
-    <t xml:space="preserve">B. Кріплення на арці — лаги на баласті</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arch roof mounting — rails on ballast</t>
+    <t xml:space="preserve">B. Кріплення на арці — «Лага 0°»: лаги на баласті, шпилькова тяга, крайні профілі</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arch roof mounting — "Rail 0°": rails on ballast, rod ties, edge profiles</t>
   </si>
   <si>
     <t xml:space="preserve">B1</t>
   </si>
   <si>
-    <t xml:space="preserve">Лага 41×41×1,5 перфорована оцинкована (4 800 і 2 400 мм)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rail 41×41×1.5 perforated galvanised (4800 and 2400 mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">як дах цеху, варіант Б: 5 282,7 на 1 749 модулів × 86 / as shop roof, variant B: per module × 86</t>
+    <t xml:space="preserve">Лага 41×41×1,5 перфорована оцинкована, 4 800 мм (бічні отвори Ø10,5 через 100, від торців 50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rail 41×41×1.5 perforated galvanised, 4800 mm (side holes Ø10.5 at 100, 50 from ends)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 — 2 комірки на шматок; лаги 251,6 м / 2 cells per piece</t>
   </si>
   <si>
     <t xml:space="preserve">B2</t>
   </si>
   <si>
-    <t xml:space="preserve">Гільза 200 з привареною муфтою M10×50 (ліва / права)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sleeve 200 with welded coupling M10×50 (LH / RH)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">як дах цеху, варіант Б: 1 989,8 на 1 749 модулів × 86 / as shop roof, variant B: per module × 86</t>
+    <t xml:space="preserve">Лага 41×41×1,5 перфорована оцинкована, 2 400 мм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rail 41×41×1.5 perforated galvanised, 2400 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 — непарна комірка / odd cell</t>
   </si>
   <si>
     <t xml:space="preserve">B3</t>
   </si>
   <si>
-    <t xml:space="preserve">Болт M10×60 + 2 шайби + гайка + трубка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bolt M10×60 + 2 washers + nut + tube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">як дах цеху, варіант Б: 3 979,5 на 1 749 модулів × 86 / as shop roof, variant B: per module × 86</t>
+    <t xml:space="preserve">Гільза П 45,5×35×2, 200 мм, з привареною муфтою M10×50 (ліва / права різьба)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U-sleeve 45.5×35×2, 200 mm, with welded M10×50 coupling (LH / RH thread)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60: на кожній лазі в лінії тяги, на стиках лаг / on every rail of a tie line, at rail splices</t>
   </si>
   <si>
     <t xml:space="preserve">B4</t>
   </si>
   <si>
-    <t xml:space="preserve">Шпилька M10 права / ліва різьба</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threaded rod M10 RH / LH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">як дах цеху, варіант Б: 2 202,1 на 1 749 модулів × 86 / as shop roof, variant B: per module × 86</t>
+    <t xml:space="preserve">Болт M10×60 + 2 шайби DIN 125 + гайка + трубка 14×1,75×38 (гільза до лаги)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bolt M10×60 + 2 washers DIN 125 + nut + tube 14×1.75×38 (sleeve to rail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 на гільзу: 120 / 2 per sleeve</t>
   </si>
   <si>
     <t xml:space="preserve">B5</t>
   </si>
   <si>
-    <t xml:space="preserve">Гайка M10 права</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nut M10 RH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">як дах цеху, варіант Б: 3 425,1 на 1 749 модулів × 86 / as shop roof, variant B: per module × 86</t>
+    <t xml:space="preserve">Шпилька M10 права / ліва різьба, 1 299 мм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threaded rod M10 RH / LH, 1299 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 між модулями в колонці + 3 через прохід / between modules + across passage</t>
   </si>
   <si>
     <t xml:space="preserve">B6</t>
   </si>
   <si>
+    <t xml:space="preserve">Гайка M10 права (контргайки шпильок)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nut M10 RH (rod lock nuts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 на шпильку / 2 per rod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B7</t>
+  </si>
+  <si>
     <t xml:space="preserve">Гайка M10 ліва</t>
   </si>
   <si>
     <t xml:space="preserve">Nut M10 LH</t>
   </si>
   <si>
-    <t xml:space="preserve">як дах цеху, варіант Б: 1 712,6 на 1 749 модулів × 86 / as shop roof, variant B: per module × 86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Профіль 41×41×1,5 крайній</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edge profile 41×41×1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">як дах цеху, варіант Б: 579,3 на 1 749 модулів × 86 / as shop roof, variant B: per module × 86</t>
+    <t xml:space="preserve">1 на шпильку / 1 per rod</t>
   </si>
   <si>
     <t xml:space="preserve">B8</t>
   </si>
   <si>
-    <t xml:space="preserve">Кутник 160/150, t = 8 (правий і лівий)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angle bracket 160/150, t = 8 (RH and LH)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">як дах цеху, варіант Б: 935,2 на 1 749 модулів × 86 / as shop roof, variant B: per module × 86</t>
+    <t xml:space="preserve">Профіль 41×41×1,5 крайній, 1 263 мм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edge profile 41×41×1.5, 1263 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76 на кінцях колонок + 6 через прохід / column ends + across passage</t>
   </si>
   <si>
     <t xml:space="preserve">B9</t>
   </si>
   <si>
-    <t xml:space="preserve">Болт M10×70 / M10×60 + гайка (кутники)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bolt M10×70 / M10×60 + nut (angle brackets)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">як дах цеху, варіант Б: 3 091,2 на 1 749 модулів × 86 / as shop roof, variant B: per module × 86</t>
+    <t xml:space="preserve">Кутник 160/150, t = 8, оцинкований (правий і лівий порівну)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angle bracket 160/150, t = 8, galvanised (equal RH and LH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 на профіль / 2 per profile</t>
   </si>
   <si>
     <t xml:space="preserve">B10</t>
   </si>
   <si>
-    <t xml:space="preserve">Притиск середній / Z33 під раму 33 мм з болтом і гайкою з пружиною</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid clamp / Z33 for 33 mm frame with bolt and spring nut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">як дах цеху, варіант Б: 7 622,0 на 1 749 модулів × 86 / as shop roof, variant B: per module × 86</t>
+    <t xml:space="preserve">Болт M10×70 + гайка + шайби (кутник до лаги)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bolt M10×70 + nut + washers (angle to rail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99: один на точку лаги / one per rail point</t>
   </si>
   <si>
     <t xml:space="preserve">B11</t>
   </si>
   <si>
-    <t xml:space="preserve">Болт M8×20 + шайба DIN 9021 (лага / профіль до блока)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bolt M8×20 + washer DIN 9021 (rail / profile to block)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">як дах цеху, варіант Б: 5 884,2 на 1 749 модулів × 86 / as shop roof, variant B: per module × 86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C. Кріплення «домік» 15° — нижній дах і надбудова</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dual-tilt 15° mounting — lower roof and stair house</t>
+    <t xml:space="preserve">Болт M10×60 + гайка + шайби (кутник до профілю)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bolt M10×60 + nut + washers (angle to profile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 на кутник / 2 per angle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Притиск середній під раму 33 мм, Al, з болтом M8×60 DIN 912 A2 і гайкою з пружиною</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid clamp for 33 mm frame, Al, with M8×60 DIN 912 A2 bolt and spring nut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201: 3 на довгий бік на спільній лазі / 3 per long side on a shared rail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Притиск Z33, Al, з болтом M8×25 DIN 912 A2 і гайкою з пружиною</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z33 clamp, Al, with M8×25 DIN 912 A2 bolt and spring nut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114 на крайніх лагах + 152 на крайніх профілях / on edge rails + on edge profiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Болт M8×20 + шайба DIN 9021 (лага / профіль до муфти блока)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bolt M8×20 + washer DIN 9021 (rail / profile to block coupling)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 на блок: 464 / 1 per block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Анкер від сповзання до основи покрівлі, з герметизацією</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anti-slide anchor to the roof deck, with sealing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10: ланцюжок тяг лінії не переходить гребінь — анкер на верхній лазі (правило КМ даху цеху) / tie chain does not cross the ridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. Кріплення 15° — «домік» і трикутники під одиночні модулі (нижній дах і надбудова)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15° mounting — dual-tilt and triangles for single modules (lower roof and stair house)</t>
   </si>
   <si>
     <t xml:space="preserve">C1</t>
   </si>
   <si>
-    <t xml:space="preserve">Комплект кріплення «домік» 15° на модуль: трикутники ГалКат, П-кронштейни, 4 притиски, метизи</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dual-tilt 15° mounting kit per module: GalKat triangles, U-brackets, 4 clamps, fasteners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">нижній дах 31 + надбудова 6 / lower roof 31 + stair house 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D. Кріплення на південних стінах</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South wall mounting</t>
+    <t xml:space="preserve">Лага «доміку» 41×41×1,5, 2 750 мм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dual-tilt rail 41×41×1.5, 2750 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 опор: 14 доміків × 2 / supports: domes × 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Балка 41×41×1,5, 1 450 мм (отвори шарніра і вершини — заводські)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beam 41×41×1.5, 1450 mm (hinge and apex holes factory)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 на опору / 2 per support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стійка 41×41×1,5, 365 мм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strut 41×41×1.5, 365 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 на опору / 1 per support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">П-кронштейн, нерж. 304, t = 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U-bracket, stainless 304, t = 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Болти M10 опори (2 × M10×100 шарніри, M10×140 вершина, M10×65 стійка, M10×60 кронштейн) + шайби + фланцеві гайки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support bolts M10 (2 × M10×100 hinges, M10×140 apex, M10×65 strut, M10×60 bracket) + washers + flange nuts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 на опору / 5 per support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Діагональ 41×41×1,5, 1 100 мм + 2 болти M10×20 з фланцевими гайками</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagonal 41×41×1.5, 1100 mm + 2 bolts M10×20 with flange nuts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">між сусідніми доміками ряду / between adjacent domes in a row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Притиск крайній під раму 33 мм з болтом M8 і гайкою з пружиною</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End clamp for 33 mm frame with M8 bolt and spring nut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 на панель: 112 / 4 per panel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Болт M8×20 + шайба DIN 9021 (лага до муфти блока)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bolt M8×20 + washer DIN 9021 (rail to block coupling)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 на опору / 4 per support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лага трикутника 15° 41×41×1,5, 1 550 мм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15° triangle rail 41×41×1.5, 1550 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 трикутників: 9 модулів × 2 / triangles: modules × 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Балка 41×41×1,5, 1 419 мм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beam 41×41×1.5, 1419 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 на трикутник / 1 per triangle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стійка 41×41×1,5, 448 мм (13-й отвір від шарніра)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strut 41×41×1.5, 448 mm (13th hole from hinge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">П-кронштейн під 15°, нерж. 304 (зміщений отвір під болт балки)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U-bracket for 15°, stainless 304 (shifted beam bolt hole)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Болти M10×60 (3) і M10×20 (3) трикутника + шайби + фланцеві гайки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triangle bolts M10×60 (3) and M10×20 (3) + washers + flange nuts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 на трикутник / 6 per triangle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">між трикутниками сусідніх модулів / between triangles of adjacent modules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 на модуль: 36 / 4 per module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 на трикутник / 2 per triangle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. Кріплення на південних стінах — фасадні вузли</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South wall mounting — facade nodes</t>
   </si>
   <si>
     <t xml:space="preserve">D1</t>
   </si>
   <si>
-    <t xml:space="preserve">Рейка 41×41 на стіні (суцільна на групу модулів)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wall rail 41×41 (continuous per module group)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24,5 м + 5 % / m + 5 %</t>
+    <t xml:space="preserve">Рейка 41×41×2,5 оцинкована на стіні, у розмір</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wall rail 41×41×2.5 galvanised, cut to size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 рейок, 24,5 м: на 540 мм від торців модуля / 8 rails at 540 mm from module ends</t>
   </si>
   <si>
     <t xml:space="preserve">D2</t>
   </si>
   <si>
-    <t xml:space="preserve">Кронштейн рейки до стіни з анкером, через ≤ 1,0 м</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rail-to-wall bracket with anchor, every ≤ 1.0 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 + 3 %</t>
+    <t xml:space="preserve">Кронштейн L 60×60×5 з пазом, цинк + анкер M10 + болт M10×35 з гайкою і 2 шайбами</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bracket L 60×60×5 slotted, galvanised + M10 anchor + M10×35 bolt with nut and 2 washers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28: через ≈1,2 м на спільній рейці, 2 на рейку альбомного / every ≈1.2 m</t>
   </si>
   <si>
     <t xml:space="preserve">D3</t>
   </si>
   <si>
-    <t xml:space="preserve">Притиск середній / кінцевий Al 6005-T6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid / end clamp Al 6005-T6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 + 3 %</t>
+    <t xml:space="preserve">Притиск крайній 80 мм, Al 6005-T6, під раму 33 + болт M8 і гайка з пружиною</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End clamp 80 mm, Al 6005-T6, for 33 mm frame + M8 bolt and spring nut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Притиск середній 80 мм, Al 6005-T6 + болт M8 і гайка з пружиною</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid clamp 80 mm, Al 6005-T6 + M8 bolt and spring nut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10: між модулями групи, на кожній рейці / between modules, on each rail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пластина заземлювальна під притиск</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earthing plate under clamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 на модуль / 1 per module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трос безпеки Ø3 AISI 316 у ПВХ ≈0,6 м з коушем, 2 втулками, гайкою-вушком M8 і болтом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety rope Ø3 AISI 316 in PVC ≈0.6 m with thimble, 2 ferrules, M8 eye nut and bolt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 на модуль, крізь заводський отвір рами / 1 per module through factory frame hole</t>
   </si>
   <si>
     <t xml:space="preserve">E. Кабелі DC і з'єднання стрінгів</t>
@@ -1096,9 +1345,6 @@
     <t xml:space="preserve">Bolt M8×20 + washer DIN 9021 (cross-bar to block coupling)</t>
   </si>
   <si>
-    <t xml:space="preserve">1 на опору / 1 per support</t>
-  </si>
-  <si>
     <t xml:space="preserve">F10</t>
   </si>
   <si>
@@ -1108,9 +1354,6 @@
     <t xml:space="preserve">Bolt M8×20 + spring nut + washer (tray to cross-bar)</t>
   </si>
   <si>
-    <t xml:space="preserve">2 на опору / 2 per support</t>
-  </si>
-  <si>
     <t xml:space="preserve">F11</t>
   </si>
   <si>
@@ -1270,7 +1513,7 @@
     <t xml:space="preserve">Serrated contact washer under sleeve bolts</t>
   </si>
   <si>
-    <t xml:space="preserve">як болти M10×60 / as bolts M10×60</t>
+    <t xml:space="preserve">як болти M10×60 гільз / as sleeve bolts M10×60</t>
   </si>
   <si>
     <t xml:space="preserve">H5</t>
@@ -1354,13 +1597,25 @@
     <t xml:space="preserve">J1</t>
   </si>
   <si>
-    <t xml:space="preserve">Баластний блок 300×300×60, 13 кг, з муфтою і матом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ballast block 300×300×60, 13 kg, with coupling and mat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">арка 234 + крайні профілі 42 + «домік» 148 + опори лотків 65, + 1 % / arch + edge + dual-tilt + tray supports, + 1 %</t>
+    <t xml:space="preserve">Баластний блок 300×300×60, 13 кг, з муфтою M8×30 і матом 320×320×3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ballast block 300×300×60, 13 kg, with M8×30 coupling and 320×320×3 mat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">арка 300, «домік» 112, трикутники 15° 36, опори лотків 65, + 1 % / arch, dual-tilt, 15° triangles, tray supports, + 1 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баластний блок 300×300×60 з муфтою, без мата, верх знято — під крайні профілі арки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ballast block 300×300×60 with coupling, no mat, top trimmed — under arch edge profiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 на крайній профіль: 164 + 1 % / 2 per edge profile + 1 %</t>
   </si>
   <si>
     <t xml:space="preserve">Стрінги і MPPT інвертора Deye SUN-100K-G03 / Strings and MPPT of the Deye SUN-100K-G03 inverter</t>
@@ -1618,7 +1873,7 @@
     <t xml:space="preserve">Баластних блоків до замовлення (+1 %) / Ballast blocks to order (+1 %)</t>
   </si>
   <si>
-    <t xml:space="preserve">арка — як дах цеху; «домік» — 4 на модуль; опори лотків / arch as shop roof; dual-tilt 4 per module; tray supports</t>
+    <t xml:space="preserve">кріплення модулів — 3D-модель (кожен блок), опори лотків / module mounting — 3D model (every block), tray supports</t>
   </si>
   <si>
     <t xml:space="preserve">Кабель AC інвертор → щит СЕС / AC cable inverter → PV board</t>
@@ -1657,6 +1912,12 @@
     <t xml:space="preserve">драбини 2 × 16, огородження 64, доріжки 16 / ladders 2 × 16, guardrail 64, walkways 16</t>
   </si>
   <si>
+    <t xml:space="preserve">Анкерів від сповзання на арці / Anti-slide anchors on the arch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ланцюжок тяг лінії не переходить гребінь — анкер на верхній лазі (правило КМ даху цеху) / tie chain not crossing the ridge</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ставки і ціни / Rates and prices</t>
   </si>
   <si>
@@ -1756,16 +2017,16 @@
     <t xml:space="preserve">рішення власника 26.10 / owner decision 26.10</t>
   </si>
   <si>
-    <t xml:space="preserve">Блоків на модуль арки / Blocks per arch module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">кошторис під ключ 27.10 / turnkey estimate 27.10, поз. 4.1–4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Блоків на модуль «доміку» / Blocks per dual-tilt module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 опори на модуль / 4 supports per module</t>
+    <t xml:space="preserve">Блоків під кріплення модулів — 3D-модель / Blocks under module mounting — 3D model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">арка 300 з матом і 164 без мата під крайні профілі, «домік» 112, трикутники 15° 36 / arch, edge profiles, dual-tilt, 15° triangles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">у т. ч. без мата під крайні профілі арки / incl. without mat under arch edge profiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">antares/abk/mount.py</t>
   </si>
   <si>
     <t xml:space="preserve">Доставка матеріалів України, на блок / Ukrainian materials delivery, per block</t>
@@ -1817,6 +2078,12 @@
   </si>
   <si>
     <t xml:space="preserve">паспорт Deye SUN-70~110K-G03 (deye.com): Euro 98,2 %, макс. 98,8 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Анкер від сповзання з герметизацією, Україна / Anti-slide anchor with sealing, Ukraine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">кошторис СЕС і УЗЕ 26.10, позиція «Анкер від сповзання» / estimate 26.10</t>
   </si>
   <si>
     <t xml:space="preserve">Інвертор Deye SUN-100K-G03</t>
@@ -1859,7 +2126,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\(#,##0.##\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\);\-"/>
@@ -1873,6 +2140,7 @@
     <numFmt numFmtId="174" formatCode="#,##0"/>
     <numFmt numFmtId="175" formatCode="0.0"/>
     <numFmt numFmtId="176" formatCode="0.000"/>
+    <numFmt numFmtId="177" formatCode="0"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -2272,7 +2540,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2528,7 +2796,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.51"/>
@@ -2619,7 +2887,7 @@
         <v>135</v>
       </c>
       <c r="F7" s="12" t="n">
-        <f aca="false">Параметри!$B$30</f>
+        <f aca="false">Параметри!$B$31</f>
         <v>73</v>
       </c>
       <c r="G7" s="13" t="n">
@@ -2651,7 +2919,7 @@
         <v>86</v>
       </c>
       <c r="F8" s="12" t="n">
-        <f aca="false">Параметри!$B$31</f>
+        <f aca="false">Параметри!$B$32</f>
         <v>11.1688311688312</v>
       </c>
       <c r="G8" s="13" t="n">
@@ -2665,7 +2933,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
         <v>24</v>
       </c>
@@ -2683,7 +2951,7 @@
         <v>37</v>
       </c>
       <c r="F9" s="12" t="n">
-        <f aca="false">Параметри!$B$32</f>
+        <f aca="false">Параметри!$B$33</f>
         <v>10.897619047619</v>
       </c>
       <c r="G9" s="13" t="n">
@@ -2715,7 +2983,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="12" t="n">
-        <f aca="false">Параметри!$B$33</f>
+        <f aca="false">Параметри!$B$34</f>
         <v>8.6026936026936</v>
       </c>
       <c r="G10" s="13" t="n">
@@ -2747,7 +3015,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="12" t="n">
-        <f aca="false">Параметри!$B$34</f>
+        <f aca="false">Параметри!$B$35</f>
         <v>60</v>
       </c>
       <c r="G11" s="13" t="n">
@@ -2779,7 +3047,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="12" t="n">
-        <f aca="false">Параметри!$B$35</f>
+        <f aca="false">Параметри!$B$36</f>
         <v>64.5729166666667</v>
       </c>
       <c r="G12" s="13" t="n">
@@ -2811,7 +3079,7 @@
         <v>132</v>
       </c>
       <c r="F13" s="12" t="n">
-        <f aca="false">Параметри!$B$36</f>
+        <f aca="false">Параметри!$B$37</f>
         <v>1.13636363636364</v>
       </c>
       <c r="G13" s="13" t="n">
@@ -2843,7 +3111,7 @@
         <v>55</v>
       </c>
       <c r="F14" s="16" t="n">
-        <f aca="false">Параметри!$B$37</f>
+        <f aca="false">Параметри!$B$38</f>
         <v>0.262857142857143</v>
       </c>
       <c r="G14" s="13" t="n">
@@ -2903,7 +3171,7 @@
       <c r="D17" s="8"/>
       <c r="E17" s="21"/>
       <c r="F17" s="22" t="n">
-        <f aca="false">Параметри!$B$38</f>
+        <f aca="false">Параметри!$B$39</f>
         <v>0.05</v>
       </c>
       <c r="G17" s="13"/>
@@ -2966,7 +3234,7 @@
         <v>135</v>
       </c>
       <c r="F20" s="12" t="n">
-        <f aca="false">Параметри!$B$39</f>
+        <f aca="false">Параметри!$B$40</f>
         <v>11.7845117845118</v>
       </c>
       <c r="G20" s="13"/>
@@ -2996,7 +3264,7 @@
         <v>132</v>
       </c>
       <c r="F21" s="12" t="n">
-        <f aca="false">Параметри!$B$40</f>
+        <f aca="false">Параметри!$B$41</f>
         <v>6.62878787878788</v>
       </c>
       <c r="G21" s="13"/>
@@ -3021,7 +3289,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="21"/>
       <c r="F22" s="22" t="n">
-        <f aca="false">Параметри!$B$41</f>
+        <f aca="false">Параметри!$B$42</f>
         <v>0.003</v>
       </c>
       <c r="G22" s="13"/>
@@ -3046,7 +3314,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="21"/>
       <c r="F23" s="23" t="n">
-        <f aca="false">Параметри!$B$42</f>
+        <f aca="false">Параметри!$B$43</f>
         <v>1.14313318257672</v>
       </c>
       <c r="G23" s="13"/>
@@ -3108,7 +3376,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="12" t="n">
-        <f aca="false">Параметри!$B$56/(1+Параметри!$B$53)/Параметри!$B$28</f>
+        <f aca="false">Параметри!$B$58/(1+Параметри!$B$54)/Параметри!$B$29</f>
         <v>2595.77114427861</v>
       </c>
       <c r="G26" s="13"/>
@@ -3120,7 +3388,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
         <v>86</v>
       </c>
@@ -3135,16 +3403,16 @@
       </c>
       <c r="E27" s="11" t="n">
         <f aca="false">Параметри!B16</f>
-        <v>494</v>
+        <v>684</v>
       </c>
       <c r="F27" s="12" t="n">
-        <f aca="false">Параметри!$B$43</f>
+        <f aca="false">Параметри!$B$44</f>
         <v>3</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="14" t="n">
         <f aca="false">E27*F27</f>
-        <v>1482</v>
+        <v>2052</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>89</v>
@@ -3168,7 +3436,7 @@
         <v>45</v>
       </c>
       <c r="F28" s="12" t="n">
-        <f aca="false">Параметри!$B$57/(1+Параметри!$B$53)/Параметри!$B$28</f>
+        <f aca="false">Параметри!$B$59/(1+Параметри!$B$54)/Параметри!$B$29</f>
         <v>59.8544590480434</v>
       </c>
       <c r="G28" s="13"/>
@@ -3197,7 +3465,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="12" t="n">
-        <f aca="false">Параметри!$B$58/(1+Параметри!$B$53)/Параметри!$B$28+Параметри!$B$59/(1+Параметри!$B$53)/Параметри!$B$28</f>
+        <f aca="false">Параметри!$B$60/(1+Параметри!$B$54)/Параметри!$B$29+Параметри!$B$61/(1+Параметри!$B$54)/Параметри!$B$29</f>
         <v>296.629167594862</v>
       </c>
       <c r="G29" s="13"/>
@@ -3226,7 +3494,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="12" t="n">
-        <f aca="false">Параметри!$B$64/(1+Параметри!$B$53)/Параметри!$B$28</f>
+        <f aca="false">Параметри!$B$66/(1+Параметри!$B$54)/Параметри!$B$29</f>
         <v>123.870201232643</v>
       </c>
       <c r="G30" s="13"/>
@@ -3255,7 +3523,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="12" t="n">
-        <f aca="false">Параметри!$B$60/(1+Параметри!$B$53)/Параметри!$B$28</f>
+        <f aca="false">Параметри!$B$62/(1+Параметри!$B$54)/Параметри!$B$29</f>
         <v>131.729412638301</v>
       </c>
       <c r="G31" s="13"/>
@@ -3282,16 +3550,16 @@
       </c>
       <c r="E32" s="11" t="n">
         <f aca="false">Параметри!B16</f>
-        <v>494</v>
+        <v>684</v>
       </c>
       <c r="F32" s="12" t="n">
-        <f aca="false">Параметри!$B$46</f>
+        <f aca="false">Параметри!$B$47</f>
         <v>0.338365183876666</v>
       </c>
       <c r="G32" s="13"/>
       <c r="H32" s="14" t="n">
         <f aca="false">E32*F32</f>
-        <v>167.152400835073</v>
+        <v>231.44178577164</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>111</v>
@@ -3315,7 +3583,7 @@
         <v>5.8</v>
       </c>
       <c r="F33" s="12" t="n">
-        <f aca="false">Параметри!$B$61/(1+Параметри!$B$53)/Параметри!$B$28</f>
+        <f aca="false">Параметри!$B$63/(1+Параметри!$B$54)/Параметри!$B$29</f>
         <v>167.075072399198</v>
       </c>
       <c r="G33" s="13"/>
@@ -3374,7 +3642,7 @@
         <v>5.6</v>
       </c>
       <c r="F35" s="12" t="n">
-        <f aca="false">Параметри!$B$61/(1+Параметри!$B$53)/Параметри!$B$28</f>
+        <f aca="false">Параметри!$B$63/(1+Параметри!$B$54)/Параметри!$B$29</f>
         <v>167.075072399198</v>
       </c>
       <c r="G35" s="13"/>
@@ -3404,7 +3672,7 @@
         <v>99</v>
       </c>
       <c r="F36" s="12" t="n">
-        <f aca="false">Параметри!$B$62/(1+Параметри!$B$53)/Параметри!$B$28</f>
+        <f aca="false">Параметри!$B$64/(1+Параметри!$B$54)/Параметри!$B$29</f>
         <v>13.324237023836</v>
       </c>
       <c r="G36" s="13"/>
@@ -3434,7 +3702,7 @@
         <v>63</v>
       </c>
       <c r="F37" s="12" t="n">
-        <f aca="false">Параметри!$B$63/(1+Параметри!$B$53)/Параметри!$B$28</f>
+        <f aca="false">Параметри!$B$65/(1+Параметри!$B$54)/Параметри!$B$29</f>
         <v>20.2346476572362</v>
       </c>
       <c r="G37" s="13"/>
@@ -3447,99 +3715,99 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="17"/>
-      <c r="B38" s="18" t="s">
+      <c r="A38" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="B38" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="20" t="n">
-        <f aca="false">SUM(H26:H37)</f>
-        <v>11989.1410768579</v>
-      </c>
-      <c r="I38" s="17"/>
+      <c r="C38" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <f aca="false">Параметри!B25</f>
+        <v>10</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <f aca="false">Параметри!$B$57</f>
+        <v>44.99</v>
+      </c>
+      <c r="G38" s="13"/>
+      <c r="H38" s="14" t="n">
+        <f aca="false">E38*F38</f>
+        <v>449.9</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-    </row>
-    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
+      <c r="A39" s="17"/>
+      <c r="B39" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="C39" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="20" t="n">
+        <f aca="false">SUM(H26:H38)</f>
+        <v>13073.3304617945</v>
+      </c>
+      <c r="I39" s="17"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="B40" s="6"/>
+      <c r="C40" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="11" t="n">
         <f aca="false">Параметри!B11</f>
         <v>96.36</v>
       </c>
-      <c r="F40" s="12" t="n">
-        <f aca="false">Параметри!$B$47</f>
-        <v>50</v>
-      </c>
-      <c r="G40" s="13"/>
-      <c r="H40" s="14" t="n">
-        <f aca="false">E40*F40</f>
-        <v>4818</v>
-      </c>
-      <c r="I40" s="15" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <f aca="false">Параметри!B9</f>
-        <v>132</v>
-      </c>
       <c r="F41" s="12" t="n">
         <f aca="false">Параметри!$B$48</f>
-        <v>1.45833333333333</v>
+        <v>50</v>
       </c>
       <c r="G41" s="13"/>
       <c r="H41" s="14" t="n">
         <f aca="false">E41*F41</f>
-        <v>192.5</v>
+        <v>4818</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
         <v>144</v>
       </c>
@@ -3558,12 +3826,12 @@
       </c>
       <c r="F42" s="12" t="n">
         <f aca="false">Параметри!$B$49</f>
-        <v>1.22348484848485</v>
+        <v>1.45833333333333</v>
       </c>
       <c r="G42" s="13"/>
       <c r="H42" s="14" t="n">
         <f aca="false">E42*F42</f>
-        <v>161.5</v>
+        <v>192.5</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>147</v>
@@ -3580,100 +3848,105 @@
         <v>150</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="E43" s="11" t="n">
-        <f aca="false">Параметри!B24</f>
-        <v>112</v>
+        <f aca="false">Параметри!B9</f>
+        <v>132</v>
       </c>
       <c r="F43" s="12" t="n">
-        <f aca="false">Параметри!$B$50/Параметри!$B$28</f>
-        <v>15.5936734239252</v>
+        <f aca="false">Параметри!$B$50</f>
+        <v>1.22348484848485</v>
       </c>
       <c r="G43" s="13"/>
       <c r="H43" s="14" t="n">
         <f aca="false">E43*F43</f>
+        <v>161.5</v>
+      </c>
+      <c r="I43" s="15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <f aca="false">Параметри!B24</f>
+        <v>112</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <f aca="false">Параметри!$B$51/Параметри!$B$29</f>
+        <v>15.5936734239252</v>
+      </c>
+      <c r="G44" s="13"/>
+      <c r="H44" s="14" t="n">
+        <f aca="false">E44*F44</f>
         <v>1746.49142347962</v>
       </c>
-      <c r="I43" s="15" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="17"/>
-      <c r="B44" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="20" t="n">
-        <f aca="false">SUM(H40:H43)</f>
+      <c r="I44" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17"/>
+      <c r="B45" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="20" t="n">
+        <f aca="false">SUM(H41:H44)</f>
         <v>6918.49142347962</v>
       </c>
-      <c r="I44" s="17"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="26"/>
-      <c r="B46" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="C46" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="29" t="n">
-        <f aca="false">H15+H18+H24+H38+H44</f>
-        <v>34929.6968570101</v>
-      </c>
-      <c r="I46" s="26"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
+      <c r="I45" s="17"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="26"/>
+      <c r="B47" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="29" t="n">
+        <f aca="false">H15+H18+H24+H39+H45</f>
+        <v>36013.8862419466</v>
+      </c>
+      <c r="I47" s="26"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C49" s="10" t="s">
+      <c r="A49" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D49" s="8"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="22" t="n">
-        <f aca="false">Параметри!$B$51</f>
-        <v>0.04</v>
-      </c>
-      <c r="G49" s="13"/>
-      <c r="H49" s="14" t="n">
-        <f aca="false">H46*F49</f>
-        <v>1397.1878742804</v>
-      </c>
-      <c r="I49" s="15" t="s">
+      <c r="B49" s="6"/>
+      <c r="C49" s="7" t="s">
         <v>162</v>
       </c>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
@@ -3689,441 +3962,465 @@
       <c r="E50" s="21"/>
       <c r="F50" s="22" t="n">
         <f aca="false">Параметри!$B$52</f>
-        <v>0.18</v>
+        <v>0.04</v>
       </c>
       <c r="G50" s="13"/>
       <c r="H50" s="14" t="n">
-        <f aca="false">H46*F50</f>
-        <v>6287.34543426181</v>
+        <f aca="false">H47*F50</f>
+        <v>1440.55544967787</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="17"/>
-      <c r="B51" s="18" t="s">
+      <c r="A51" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51" s="8"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="22" t="n">
+        <f aca="false">Параметри!$B$53</f>
+        <v>0.18</v>
+      </c>
+      <c r="G51" s="13"/>
+      <c r="H51" s="14" t="n">
+        <f aca="false">H47*F51</f>
+        <v>6482.49952355039</v>
+      </c>
+      <c r="I51" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C51" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="20" t="n">
-        <f aca="false">H49+H50</f>
-        <v>7684.53330854221</v>
-      </c>
-      <c r="I51" s="17"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="26"/>
-      <c r="B53" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C53" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="29" t="n">
-        <f aca="false">H46+H51</f>
-        <v>42614.2301655523</v>
-      </c>
-      <c r="I53" s="26"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="17"/>
+      <c r="B52" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="20" t="n">
+        <f aca="false">H50+H51</f>
+        <v>7923.05497322826</v>
+      </c>
+      <c r="I52" s="17"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="17"/>
-      <c r="B54" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="20" t="n">
-        <f aca="false">H53*Параметри!$B$53</f>
-        <v>8522.84603311046</v>
-      </c>
-      <c r="I54" s="17"/>
+      <c r="A54" s="26"/>
+      <c r="B54" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C54" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="29" t="n">
+        <f aca="false">H47+H52</f>
+        <v>43936.9412151749</v>
+      </c>
+      <c r="I54" s="26"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="26"/>
-      <c r="B55" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="C55" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="26"/>
-      <c r="G55" s="26"/>
-      <c r="H55" s="29" t="n">
-        <f aca="false">H53+H54</f>
-        <v>51137.0761986627</v>
-      </c>
-      <c r="I55" s="26"/>
-    </row>
-    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="17"/>
-      <c r="B57" s="18" t="s">
+      <c r="A55" s="17"/>
+      <c r="B55" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C55" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="20" t="n">
-        <f aca="false">(H53-H7)*Параметри!$B$53</f>
-        <v>6551.84603311046</v>
-      </c>
-      <c r="I57" s="17"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="26"/>
-      <c r="B58" s="27" t="s">
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="20" t="n">
+        <f aca="false">H54*Параметри!$B$54</f>
+        <v>8787.38824303498</v>
+      </c>
+      <c r="I55" s="17"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="26"/>
+      <c r="B56" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="C58" s="28" t="s">
+      <c r="C56" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="D58" s="26"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
-      <c r="H58" s="29" t="n">
-        <f aca="false">H53+H57</f>
-        <v>49166.0761986627</v>
-      </c>
-      <c r="I58" s="26"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="17"/>
-      <c r="B60" s="18" t="s">
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="29" t="n">
+        <f aca="false">H54+H55</f>
+        <v>52724.3294582099</v>
+      </c>
+      <c r="I56" s="26"/>
+    </row>
+    <row r="58" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="17"/>
+      <c r="B58" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="C60" s="19" t="s">
+      <c r="C58" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="20" t="n">
-        <f aca="false">H53/Параметри!B11</f>
-        <v>442.239831522958</v>
-      </c>
-      <c r="I60" s="17"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="20" t="n">
+        <f aca="false">(H54-H7)*Параметри!$B$54</f>
+        <v>6816.38824303498</v>
+      </c>
+      <c r="I58" s="17"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="26"/>
+      <c r="B59" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="B62" s="6"/>
-      <c r="C62" s="7" t="s">
+      <c r="C59" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="29" t="n">
+        <f aca="false">H54+H58</f>
+        <v>50753.3294582099</v>
+      </c>
+      <c r="I59" s="26"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="17"/>
+      <c r="B61" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="20" t="n">
+        <f aca="false">H54/Параметри!B11</f>
+        <v>455.966596255447</v>
+      </c>
+      <c r="I61" s="17"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="17"/>
-      <c r="B63" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="C63" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="E63" s="17"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="31" t="n">
-        <f aca="false">Параметри!B11</f>
-        <v>96.36</v>
-      </c>
-      <c r="I63" s="17"/>
+      <c r="A63" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" s="6"/>
+      <c r="C63" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="17"/>
       <c r="B64" s="8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>186</v>
+        <v>143</v>
       </c>
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
       <c r="G64" s="17"/>
-      <c r="H64" s="32" t="n">
-        <f aca="false">Параметри!B14</f>
-        <v>87.1</v>
+      <c r="H64" s="31" t="n">
+        <f aca="false">Параметри!B11</f>
+        <v>96.36</v>
       </c>
       <c r="I64" s="17"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="17"/>
       <c r="B65" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C65" s="30" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E65" s="17"/>
       <c r="F65" s="17"/>
       <c r="G65" s="17"/>
       <c r="H65" s="32" t="n">
-        <f aca="false">H64*Параметри!$B$55</f>
-        <v>85.5322</v>
+        <f aca="false">Параметри!B14</f>
+        <v>87.1</v>
       </c>
       <c r="I65" s="17"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="17"/>
       <c r="B66" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C66" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="D66" s="8" t="s">
         <v>190</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>191</v>
       </c>
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
       <c r="G66" s="17"/>
-      <c r="H66" s="33" t="n">
-        <f aca="false">H65*1000/H63</f>
-        <v>887.631797426318</v>
+      <c r="H66" s="32" t="n">
+        <f aca="false">H65*Параметри!$B$56</f>
+        <v>85.5322</v>
       </c>
       <c r="I66" s="17"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="17"/>
       <c r="B67" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E67" s="17"/>
       <c r="F67" s="17"/>
       <c r="G67" s="17"/>
-      <c r="H67" s="34" t="n">
-        <f aca="false">Параметри!$B$54/(1+Параметри!$B$53)/Параметри!$B$28</f>
-        <v>0.12994727853271</v>
+      <c r="H67" s="33" t="n">
+        <f aca="false">H66*1000/H64</f>
+        <v>887.631797426318</v>
       </c>
       <c r="I67" s="17"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="17"/>
       <c r="B68" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C68" s="30" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="17"/>
-      <c r="H68" s="14" t="n">
-        <f aca="false">H65*1000*H67</f>
-        <v>11114.6766169154</v>
+      <c r="H68" s="34" t="n">
+        <f aca="false">Параметри!$B$55/(1+Параметри!$B$54)/Параметри!$B$29</f>
+        <v>0.12994727853271</v>
       </c>
       <c r="I68" s="17"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="17"/>
       <c r="B69" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
       <c r="G69" s="17"/>
-      <c r="H69" s="35" t="n">
-        <f aca="false">H53/H68</f>
-        <v>3.83405038529845</v>
+      <c r="H69" s="14" t="n">
+        <f aca="false">H66*1000*H68</f>
+        <v>11114.6766169154</v>
       </c>
       <c r="I69" s="17"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="17"/>
       <c r="B70" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E70" s="17"/>
       <c r="F70" s="17"/>
       <c r="G70" s="17"/>
-      <c r="H70" s="14" t="n">
-        <f aca="false">H53/H65</f>
-        <v>498.224413326821</v>
+      <c r="H70" s="35" t="n">
+        <f aca="false">H54/H69</f>
+        <v>3.95305619133419</v>
       </c>
       <c r="I70" s="17"/>
     </row>
-    <row r="72" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B72" s="36" t="s">
-        <v>203</v>
-      </c>
-      <c r="C72" s="36"/>
-      <c r="D72" s="36"/>
-      <c r="E72" s="36"/>
-      <c r="F72" s="36"/>
-      <c r="G72" s="36"/>
-      <c r="H72" s="36"/>
-      <c r="I72" s="36"/>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="17"/>
+      <c r="B71" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="C71" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="14" t="n">
+        <f aca="false">H54/H66</f>
+        <v>513.688893950756</v>
+      </c>
+      <c r="I71" s="17"/>
     </row>
     <row r="73" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B73" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
+      <c r="B73" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="C73" s="36"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="36"/>
+      <c r="G73" s="36"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="36"/>
     </row>
     <row r="74" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B74" s="36" t="s">
-        <v>205</v>
-      </c>
-      <c r="C74" s="36"/>
-      <c r="D74" s="36"/>
-      <c r="E74" s="36"/>
-      <c r="F74" s="36"/>
-      <c r="G74" s="36"/>
-      <c r="H74" s="36"/>
-      <c r="I74" s="36"/>
+      <c r="B74" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="37"/>
+      <c r="I74" s="37"/>
     </row>
     <row r="75" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B75" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
+      <c r="B75" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="C75" s="36"/>
+      <c r="D75" s="36"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="36"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="36"/>
     </row>
     <row r="76" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B76" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="C76" s="36"/>
-      <c r="D76" s="36"/>
-      <c r="E76" s="36"/>
-      <c r="F76" s="36"/>
-      <c r="G76" s="36"/>
-      <c r="H76" s="36"/>
-      <c r="I76" s="36"/>
+      <c r="B76" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="37"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="37"/>
+      <c r="H76" s="37"/>
+      <c r="I76" s="37"/>
     </row>
     <row r="77" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B77" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37"/>
-      <c r="I77" s="37"/>
+      <c r="B77" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="C77" s="36"/>
+      <c r="D77" s="36"/>
+      <c r="E77" s="36"/>
+      <c r="F77" s="36"/>
+      <c r="G77" s="36"/>
+      <c r="H77" s="36"/>
+      <c r="I77" s="36"/>
     </row>
     <row r="78" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B78" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-      <c r="G78" s="36"/>
-      <c r="H78" s="36"/>
-      <c r="I78" s="36"/>
+      <c r="B78" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="C78" s="37"/>
+      <c r="D78" s="37"/>
+      <c r="E78" s="37"/>
+      <c r="F78" s="37"/>
+      <c r="G78" s="37"/>
+      <c r="H78" s="37"/>
+      <c r="I78" s="37"/>
     </row>
     <row r="79" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B79" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="C79" s="37"/>
-      <c r="D79" s="37"/>
-      <c r="E79" s="37"/>
-      <c r="F79" s="37"/>
-      <c r="G79" s="37"/>
-      <c r="H79" s="37"/>
-      <c r="I79" s="37"/>
+      <c r="B79" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="C79" s="36"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="36"/>
+      <c r="G79" s="36"/>
+      <c r="H79" s="36"/>
+      <c r="I79" s="36"/>
     </row>
     <row r="80" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B80" s="36" t="s">
-        <v>211</v>
-      </c>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="36"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
+      <c r="B80" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="C80" s="37"/>
+      <c r="D80" s="37"/>
+      <c r="E80" s="37"/>
+      <c r="F80" s="37"/>
+      <c r="G80" s="37"/>
+      <c r="H80" s="37"/>
+      <c r="I80" s="37"/>
     </row>
     <row r="81" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B81" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="C81" s="37"/>
-      <c r="D81" s="37"/>
-      <c r="E81" s="37"/>
-      <c r="F81" s="37"/>
-      <c r="G81" s="37"/>
-      <c r="H81" s="37"/>
-      <c r="I81" s="37"/>
+      <c r="B81" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="C81" s="36"/>
+      <c r="D81" s="36"/>
+      <c r="E81" s="36"/>
+      <c r="F81" s="36"/>
+      <c r="G81" s="36"/>
+      <c r="H81" s="36"/>
+      <c r="I81" s="36"/>
+    </row>
+    <row r="82" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B82" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="C82" s="37"/>
+      <c r="D82" s="37"/>
+      <c r="E82" s="37"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="37"/>
+      <c r="H82" s="37"/>
+      <c r="I82" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B72:I72"/>
     <mergeCell ref="B73:I73"/>
     <mergeCell ref="B74:I74"/>
     <mergeCell ref="B75:I75"/>
@@ -4133,6 +4430,7 @@
     <mergeCell ref="B79:I79"/>
     <mergeCell ref="B80:I80"/>
     <mergeCell ref="B81:I81"/>
+    <mergeCell ref="B82:I82"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4149,7 +4447,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -4163,12 +4461,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4188,19 +4486,19 @@
         <v>7</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="7" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -4209,13 +4507,13 @@
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>17</v>
@@ -4227,847 +4525,877 @@
         <v>14</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="7" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
     </row>
-    <row r="8" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>260</v>
+        <v>37</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>19</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="F9" s="38" t="s">
         <v>19</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>196</v>
+        <v>62</v>
       </c>
       <c r="F10" s="38" t="s">
         <v>19</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="F11" s="38" t="s">
         <v>19</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>169</v>
+        <v>54</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>19</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>19</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="F15" s="38" t="s">
         <v>19</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>19</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>375</v>
+        <v>104</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>97</v>
       </c>
       <c r="E18" s="24" t="n">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>212</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D20" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>280</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D21" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="E20" s="24" t="n">
-        <v>37</v>
-      </c>
-      <c r="F20" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E21" s="24" t="n">
+        <v>488</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E22" s="24" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="24" t="n">
-        <v>33</v>
-      </c>
-      <c r="F23" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>284</v>
-      </c>
+      <c r="A23" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E24" s="24" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
+      <c r="A25" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="24" t="n">
+        <v>58</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E26" s="24" t="n">
-        <v>430</v>
+        <v>29</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E27" s="24" t="n">
-        <v>650</v>
+        <v>29</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>302</v>
+        <v>97</v>
       </c>
       <c r="E28" s="24" t="n">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E29" s="24" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="17" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D30" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E30" s="24" t="n">
-        <v>42</v>
+        <v>118</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>315</v>
+        <v>97</v>
       </c>
       <c r="E31" s="24" t="n">
-        <v>9</v>
+        <v>118</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D32" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="24" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="A33" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E34" s="24" t="n">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="D35" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E35" s="24" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="E36" s="24" t="n">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="D37" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E37" s="24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="D38" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E38" s="24" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>343</v>
+        <v>319</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="E39" s="24" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G39" s="15" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="6"/>
+      <c r="C40" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D40" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" s="24" t="n">
-        <v>103</v>
-      </c>
-      <c r="F40" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G40" s="15" t="s">
+      <c r="B41" s="9" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17" t="s">
+      <c r="C41" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="D41" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" s="24" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="G41" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="C41" s="10" t="s">
+    </row>
+    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="D41" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" s="24" t="n">
-        <v>65</v>
-      </c>
-      <c r="F41" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G41" s="15" t="s">
+      <c r="B42" s="9" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17" t="s">
+      <c r="C42" s="10" t="s">
         <v>354</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>356</v>
       </c>
       <c r="D42" s="17" t="s">
         <v>97</v>
       </c>
       <c r="E42" s="24" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G42" s="15" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="B43" s="9" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="17" t="s">
+      <c r="C43" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="D43" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="F43" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="G43" s="15" t="s">
         <v>359</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="D43" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="E43" s="24" t="n">
-        <v>130</v>
-      </c>
-      <c r="F43" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G43" s="15" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C44" s="10" t="s">
         <v>362</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>364</v>
       </c>
       <c r="D44" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E44" s="24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G44" s="15" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="B45" s="9" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="s">
+      <c r="C45" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="7" t="s">
+      <c r="D45" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="F45" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="G45" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-    </row>
-    <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="17" t="s">
         <v>368</v>
       </c>
@@ -5078,40 +5406,30 @@
         <v>370</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="E46" s="24" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="G46" s="15" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="17" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="B47" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D47" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E47" s="24" t="n">
-        <v>45</v>
-      </c>
-      <c r="F47" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="G47" s="15" t="s">
+      <c r="B47" s="6"/>
+      <c r="C47" s="7" t="s">
         <v>373</v>
       </c>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="17" t="s">
@@ -5124,19 +5442,19 @@
         <v>376</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E48" s="24" t="n">
-        <v>10</v>
+        <v>430</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="G48" s="15" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="17" t="s">
         <v>378</v>
       </c>
@@ -5147,19 +5465,19 @@
         <v>380</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E49" s="24" t="n">
-        <v>1</v>
+        <v>650</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="G49" s="15" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
         <v>382</v>
       </c>
@@ -5170,411 +5488,920 @@
         <v>384</v>
       </c>
       <c r="D50" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="E50" s="24" t="n">
+        <v>103</v>
+      </c>
+      <c r="F50" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G50" s="15" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="D51" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E51" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="F51" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G51" s="15" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="D52" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E50" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="G50" s="15"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>387</v>
-      </c>
-      <c r="D51" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="G51" s="15" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="17" t="s">
-        <v>389</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>97</v>
-      </c>
       <c r="E52" s="24" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>103</v>
-      </c>
-      <c r="G52" s="15"/>
+        <v>32</v>
+      </c>
+      <c r="G52" s="15" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="17" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>48</v>
+        <v>398</v>
       </c>
       <c r="E53" s="24" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="G53" s="15" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="17" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="E54" s="24" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="G54" s="15"/>
+        <v>32</v>
+      </c>
+      <c r="G54" s="15" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="7" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
     </row>
-    <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="17" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D56" s="17" t="s">
         <v>48</v>
       </c>
       <c r="E56" s="24" t="n">
-        <v>245</v>
+        <v>117</v>
       </c>
       <c r="F56" s="38" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="17" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E57" s="24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F57" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="G57" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="G57" s="15" t="s">
+        <v>413</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="17" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D58" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="24" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G58" s="15" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="17" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D59" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E59" s="24" t="n">
-        <v>196</v>
+        <v>7</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G59" s="15" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="17" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D60" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E60" s="24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F60" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="G60" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="G60" s="15" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="17" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="D61" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E61" s="24" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F61" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="G61" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="G61" s="15" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="B62" s="6"/>
-      <c r="C62" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-    </row>
-    <row r="63" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="D62" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="24" t="n">
+        <v>103</v>
+      </c>
+      <c r="F62" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G62" s="15" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="17" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E63" s="24" t="n">
-        <v>5.8</v>
+        <v>65</v>
       </c>
       <c r="F63" s="38" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G63" s="15" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="17" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>117</v>
+        <v>438</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>118</v>
+        <v>439</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="E64" s="24" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="F64" s="38" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="G64" s="15" t="s">
-        <v>429</v>
+        <v>302</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="17" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="D65" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E65" s="24" t="n">
+        <v>130</v>
+      </c>
+      <c r="F65" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G65" s="15" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F66" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G66" s="15" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B67" s="6"/>
+      <c r="C67" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+    </row>
+    <row r="68" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="17" t="s">
+        <v>449</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="G68" s="15" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D69" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E65" s="24" t="n">
+      <c r="E69" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="F69" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="G69" s="15" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F70" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="G70" s="15" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="D71" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="G71" s="15" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="D72" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="G72" s="15"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="D73" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G73" s="15" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E74" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="G74" s="15"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="17" t="s">
+        <v>473</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E75" s="24" t="n">
+        <v>55</v>
+      </c>
+      <c r="F75" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="G75" s="15" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E76" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="G76" s="15"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B77" s="6"/>
+      <c r="C77" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="6"/>
+    </row>
+    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="17" t="s">
+        <v>482</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="D78" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E78" s="24" t="n">
+        <v>245</v>
+      </c>
+      <c r="F78" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G78" s="15" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="D79" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E79" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G79" s="15"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="D80" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="F80" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G80" s="15" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="D81" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" s="24" t="n">
+        <v>126</v>
+      </c>
+      <c r="F81" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G81" s="15" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="D82" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G82" s="15"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="17" t="s">
+        <v>500</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="D83" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G83" s="15"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="B84" s="6"/>
+      <c r="C84" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6"/>
+    </row>
+    <row r="85" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="D85" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E85" s="24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F85" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="G85" s="15" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="17" t="s">
+        <v>509</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D86" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="G86" s="15" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="D87" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E87" s="24" t="n">
         <v>5.6</v>
       </c>
-      <c r="F65" s="38" t="s">
+      <c r="F87" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="G65" s="15" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="17" t="s">
-        <v>434</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="D66" s="17" t="s">
+      <c r="G87" s="15" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="D88" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E66" s="24" t="n">
+      <c r="E88" s="24" t="n">
         <v>99</v>
       </c>
-      <c r="F66" s="38" t="s">
+      <c r="F88" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="G66" s="15" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="B67" s="9" t="s">
+      <c r="G88" s="15" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="17" t="s">
+        <v>519</v>
+      </c>
+      <c r="B89" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C89" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D89" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="E67" s="24" t="n">
+      <c r="E89" s="24" t="n">
         <v>63</v>
       </c>
-      <c r="F67" s="38" t="s">
+      <c r="F89" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="G67" s="15" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="B68" s="6"/>
-      <c r="C68" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-    </row>
-    <row r="69" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="17" t="s">
-        <v>442</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="D69" s="17" t="s">
+      <c r="G89" s="15" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="B90" s="6"/>
+      <c r="C90" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
+    </row>
+    <row r="91" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="D91" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E69" s="24" t="n">
-        <v>494</v>
-      </c>
-      <c r="F69" s="38" t="s">
+      <c r="E91" s="24" t="n">
+        <v>518</v>
+      </c>
+      <c r="F91" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="G69" s="15" t="s">
-        <v>445</v>
+      <c r="G91" s="15" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="D92" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E92" s="24" t="n">
+        <v>166</v>
+      </c>
+      <c r="F92" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="G92" s="15" t="s">
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -5610,17 +6437,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>446</v>
+        <v>531</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>447</v>
+        <v>532</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>448</v>
+        <v>533</v>
       </c>
       <c r="B4" s="39" t="n">
         <v>49.5</v>
@@ -5628,7 +6455,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>449</v>
+        <v>534</v>
       </c>
       <c r="B5" s="39" t="n">
         <v>-0.25</v>
@@ -5636,7 +6463,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>450</v>
+        <v>535</v>
       </c>
       <c r="B6" s="39" t="n">
         <v>-30</v>
@@ -5644,7 +6471,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>451</v>
+        <v>536</v>
       </c>
       <c r="B7" s="39" t="n">
         <v>37</v>
@@ -5652,7 +6479,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>452</v>
+        <v>537</v>
       </c>
       <c r="B8" s="39" t="n">
         <v>45.93</v>
@@ -5660,7 +6487,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>453</v>
+        <v>538</v>
       </c>
       <c r="B9" s="39" t="n">
         <v>17.51</v>
@@ -5668,7 +6495,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>454</v>
+        <v>539</v>
       </c>
       <c r="B10" s="39" t="n">
         <v>18.51</v>
@@ -5676,7 +6503,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>455</v>
+        <v>540</v>
       </c>
       <c r="B11" s="39" t="n">
         <v>1000</v>
@@ -5684,7 +6511,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>456</v>
+        <v>541</v>
       </c>
       <c r="B12" s="39" t="n">
         <v>200</v>
@@ -5692,7 +6519,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>457</v>
+        <v>542</v>
       </c>
       <c r="B13" s="39" t="n">
         <v>850</v>
@@ -5700,7 +6527,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>458</v>
+        <v>543</v>
       </c>
       <c r="B14" s="39" t="n">
         <v>250</v>
@@ -5708,7 +6535,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>459</v>
+        <v>544</v>
       </c>
       <c r="B15" s="39" t="n">
         <v>40</v>
@@ -5716,7 +6543,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>460</v>
+        <v>545</v>
       </c>
       <c r="B16" s="39" t="n">
         <v>60</v>
@@ -5724,45 +6551,45 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>461</v>
+        <v>546</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>462</v>
+        <v>547</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>463</v>
+        <v>548</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>464</v>
+        <v>549</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>465</v>
+        <v>550</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>466</v>
+        <v>551</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>467</v>
+        <v>552</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>468</v>
+        <v>553</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>469</v>
+        <v>554</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>470</v>
+        <v>555</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>471</v>
+        <v>556</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>472</v>
+        <v>557</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>473</v>
+        <v>558</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">Параметри!B13</f>
@@ -5811,45 +6638,45 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>474</v>
+        <v>559</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>475</v>
+        <v>560</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>476</v>
+        <v>561</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>477</v>
+        <v>562</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>478</v>
+        <v>563</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>479</v>
+        <v>564</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>480</v>
+        <v>565</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>481</v>
+        <v>566</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>482</v>
+        <v>567</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>483</v>
+        <v>568</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>484</v>
+        <v>569</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>485</v>
+        <v>570</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>1</v>
@@ -5858,10 +6685,10 @@
         <v>12</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>486</v>
+        <v>571</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>487</v>
+        <v>572</v>
       </c>
       <c r="F22" s="39" t="n">
         <v>3.1</v>
@@ -5887,7 +6714,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>488</v>
+        <v>573</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>1</v>
@@ -5896,10 +6723,10 @@
         <v>12</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>486</v>
+        <v>571</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>487</v>
+        <v>572</v>
       </c>
       <c r="F23" s="39" t="n">
         <v>9</v>
@@ -5925,7 +6752,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>489</v>
+        <v>574</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>2</v>
@@ -5934,10 +6761,10 @@
         <v>12</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>486</v>
+        <v>571</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>487</v>
+        <v>572</v>
       </c>
       <c r="F24" s="39" t="n">
         <v>10.9</v>
@@ -5963,7 +6790,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>490</v>
+        <v>575</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>2</v>
@@ -5972,10 +6799,10 @@
         <v>12</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>491</v>
+        <v>576</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>487</v>
+        <v>572</v>
       </c>
       <c r="F25" s="39" t="n">
         <v>14</v>
@@ -6001,7 +6828,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>492</v>
+        <v>577</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>3</v>
@@ -6010,10 +6837,10 @@
         <v>12</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>486</v>
+        <v>571</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>493</v>
+        <v>578</v>
       </c>
       <c r="F26" s="39" t="n">
         <v>3.1</v>
@@ -6039,7 +6866,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>494</v>
+        <v>579</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>3</v>
@@ -6048,10 +6875,10 @@
         <v>12</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>486</v>
+        <v>571</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>493</v>
+        <v>578</v>
       </c>
       <c r="F27" s="39" t="n">
         <v>4</v>
@@ -6077,7 +6904,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>495</v>
+        <v>580</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>4</v>
@@ -6086,10 +6913,10 @@
         <v>12</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>486</v>
+        <v>571</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>493</v>
+        <v>578</v>
       </c>
       <c r="F28" s="39" t="n">
         <v>11.4</v>
@@ -6115,7 +6942,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>496</v>
+        <v>581</v>
       </c>
       <c r="B29" s="8" t="n">
         <v>4</v>
@@ -6124,10 +6951,10 @@
         <v>12</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>486</v>
+        <v>571</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>493</v>
+        <v>578</v>
       </c>
       <c r="F29" s="39" t="n">
         <v>7.7</v>
@@ -6153,7 +6980,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>497</v>
+        <v>582</v>
       </c>
       <c r="B30" s="8" t="n">
         <v>5</v>
@@ -6162,10 +6989,10 @@
         <v>12</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>498</v>
+        <v>583</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>493</v>
+        <v>578</v>
       </c>
       <c r="F30" s="39" t="n">
         <v>15</v>
@@ -6191,7 +7018,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>499</v>
+        <v>584</v>
       </c>
       <c r="B31" s="8" t="n">
         <v>5</v>
@@ -6200,10 +7027,10 @@
         <v>12</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>498</v>
+        <v>583</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>487</v>
+        <v>572</v>
       </c>
       <c r="F31" s="39" t="n">
         <v>15</v>
@@ -6229,7 +7056,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>500</v>
+        <v>585</v>
       </c>
       <c r="B32" s="8" t="n">
         <v>6</v>
@@ -6238,10 +7065,10 @@
         <v>12</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>501</v>
+        <v>586</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>502</v>
+        <v>587</v>
       </c>
       <c r="F32" s="39" t="n">
         <v>71.2</v>
@@ -6267,7 +7094,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>503</v>
+        <v>588</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="n">
@@ -6301,7 +7128,7 @@
     </row>
     <row r="35" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="36" t="s">
-        <v>504</v>
+        <v>589</v>
       </c>
       <c r="B35" s="36"/>
       <c r="C35" s="36"/>
@@ -6334,7 +7161,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="70"/>
@@ -6345,107 +7172,107 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>505</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>506</v>
+        <v>591</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>507</v>
+        <v>592</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>508</v>
+        <v>593</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>509</v>
+        <v>594</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>510</v>
+        <v>595</v>
       </c>
       <c r="B5" s="24" t="n">
         <v>86</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>511</v>
+        <v>596</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>512</v>
+        <v>597</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>513</v>
+        <v>598</v>
       </c>
       <c r="B6" s="24" t="n">
         <v>31</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>511</v>
+        <v>596</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>514</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>515</v>
+        <v>600</v>
       </c>
       <c r="B7" s="24" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>511</v>
+        <v>596</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>516</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>517</v>
+        <v>602</v>
       </c>
       <c r="B8" s="24" t="n">
         <v>9</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>511</v>
+        <v>596</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>516</v>
+        <v>601</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>518</v>
+        <v>603</v>
       </c>
       <c r="B9" s="21" t="n">
         <f aca="false">B5+B6+B7+B8</f>
         <v>132</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>511</v>
+        <v>596</v>
       </c>
       <c r="D9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>519</v>
+        <v>604</v>
       </c>
       <c r="B10" s="21" t="n">
-        <f aca="false">ROUNDUP(B9*$B$29,0)</f>
+        <f aca="false">ROUNDUP(B9*$B$30,0)</f>
         <v>135</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>511</v>
+        <v>596</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>73</v>
@@ -6453,747 +7280,774 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>520</v>
+        <v>605</v>
       </c>
       <c r="B11" s="31" t="n">
-        <f aca="false">B9*$B$27/1000</f>
+        <f aca="false">B9*$B$28/1000</f>
         <v>96.36</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>521</v>
+        <v>606</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>522</v>
+        <v>607</v>
       </c>
       <c r="B12" s="24" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>511</v>
+        <v>596</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>523</v>
+        <v>608</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>524</v>
+        <v>609</v>
       </c>
       <c r="B13" s="24" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>511</v>
+        <v>596</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>525</v>
+        <v>610</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>526</v>
+        <v>611</v>
       </c>
       <c r="B14" s="45" t="n">
         <v>87.1</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>527</v>
+        <v>612</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>528</v>
+        <v>613</v>
       </c>
       <c r="B15" s="24" t="n">
         <v>65</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>511</v>
+        <v>596</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>530</v>
+        <v>615</v>
       </c>
       <c r="B16" s="21" t="n">
-        <f aca="false">ROUNDUP((B5*$B$44+(B6+B7)*$B$45+B15)*1.01,0)</f>
-        <v>494</v>
+        <f aca="false">ROUNDUP(($B$45+B15)*1.01,0)</f>
+        <v>684</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>511</v>
+        <v>596</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>531</v>
+        <v>616</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>532</v>
+        <v>617</v>
       </c>
       <c r="B17" s="24" t="n">
         <v>45</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>533</v>
+        <v>618</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>373</v>
+        <v>454</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>534</v>
+        <v>619</v>
       </c>
       <c r="B18" s="24" t="n">
         <v>55</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>533</v>
+        <v>618</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>535</v>
+        <v>620</v>
       </c>
       <c r="B19" s="24" t="n">
         <v>5.8</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>533</v>
+        <v>618</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>427</v>
+        <v>508</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>536</v>
+        <v>621</v>
       </c>
       <c r="B20" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>511</v>
+        <v>596</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>429</v>
+        <v>510</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>537</v>
+        <v>622</v>
       </c>
       <c r="B21" s="24" t="n">
         <v>5.6</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>533</v>
+        <v>618</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>538</v>
+        <v>623</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>539</v>
+        <v>624</v>
       </c>
       <c r="B22" s="24" t="n">
         <v>99</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>533</v>
+        <v>618</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>437</v>
+        <v>518</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>540</v>
+        <v>625</v>
       </c>
       <c r="B23" s="24" t="n">
         <v>63</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>541</v>
+        <v>626</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>439</v>
+        <v>520</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>542</v>
+        <v>627</v>
       </c>
       <c r="B24" s="24" t="n">
         <v>112</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="46"/>
-      <c r="D25" s="46"/>
-    </row>
-    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="s">
-        <v>544</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="C26" s="4" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="46"/>
+      <c r="D26" s="46"/>
+    </row>
+    <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="47" t="s">
+        <v>631</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="47" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
-        <v>545</v>
-      </c>
-      <c r="B27" s="24" t="n">
-        <v>730</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>546</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>547</v>
+      <c r="D27" s="47" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>548</v>
-      </c>
-      <c r="B28" s="48" t="n">
-        <v>44.89</v>
+        <v>632</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>730</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>549</v>
+        <v>633</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>550</v>
+        <v>634</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="B29" s="49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="C29" s="8"/>
+        <v>635</v>
+      </c>
+      <c r="B29" s="48" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>636</v>
+      </c>
       <c r="D29" s="15" t="s">
-        <v>73</v>
+        <v>637</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="B30" s="50" t="n">
+        <v>638</v>
+      </c>
+      <c r="B30" s="49" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="15" t="s">
         <v>73</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>553</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>555</v>
-      </c>
-      <c r="B31" s="51" t="n">
+        <v>639</v>
+      </c>
+      <c r="B31" s="50" t="n">
+        <v>73</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="B32" s="51" t="n">
         <f aca="false">21500/1925</f>
         <v>11.1688311688312</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
-        <v>558</v>
-      </c>
-      <c r="B32" s="51" t="n">
+      <c r="C32" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="B33" s="51" t="n">
         <f aca="false">11211/1260+4*0.5</f>
         <v>10.897619047619</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="s">
-        <v>560</v>
-      </c>
-      <c r="B33" s="51" t="n">
+      <c r="C33" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="B34" s="51" t="n">
         <f aca="false">2555/297</f>
         <v>8.6026936026936</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="D33" s="15" t="s">
+      <c r="C34" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="D34" s="15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="B34" s="51" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="B35" s="51" t="n">
         <f aca="false">11520/192</f>
         <v>60</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>562</v>
-      </c>
-      <c r="D34" s="15" t="s">
+      <c r="C35" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="D35" s="15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
-        <v>563</v>
-      </c>
-      <c r="B35" s="51" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="B36" s="51" t="n">
         <f aca="false">12398/192</f>
         <v>64.5729166666667</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>562</v>
-      </c>
-      <c r="D35" s="15" t="s">
+      <c r="C36" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="D36" s="15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
-        <v>564</v>
-      </c>
-      <c r="B36" s="51" t="n">
+    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="B37" s="51" t="n">
         <f aca="false">2400/2112</f>
         <v>1.13636363636364</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="D36" s="15" t="s">
+      <c r="C37" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="D37" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="B37" s="34" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="B38" s="34" t="n">
         <f aca="false">276/1050</f>
         <v>0.262857142857143</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>566</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="B38" s="52" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C38" s="8"/>
+      <c r="C38" s="8" t="s">
+        <v>653</v>
+      </c>
       <c r="D38" s="15" t="s">
-        <v>569</v>
+        <v>654</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="B39" s="51" t="n">
+        <v>655</v>
+      </c>
+      <c r="B39" s="52" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="15" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="B40" s="51" t="n">
         <f aca="false">7000/594</f>
         <v>11.7845117845118</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>553</v>
-      </c>
-      <c r="D39" s="15" t="s">
+      <c r="C40" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="D40" s="15" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="B40" s="51" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="B41" s="51" t="n">
         <f aca="false">14000/2112</f>
         <v>6.62878787878788</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="D40" s="15" t="s">
+      <c r="C41" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="D41" s="15" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9" t="s">
-        <v>572</v>
-      </c>
-      <c r="B41" s="52" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="15" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="B42" s="34" t="n">
+        <v>659</v>
+      </c>
+      <c r="B42" s="52" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="C42" s="8"/>
+      <c r="D42" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="B43" s="34" t="n">
         <f aca="false">4840.7596950824/4234.64192</f>
         <v>1.14313318257672</v>
       </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="15" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9" t="s">
-        <v>575</v>
-      </c>
-      <c r="B43" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>553</v>
-      </c>
+      <c r="C43" s="8"/>
       <c r="D43" s="15" t="s">
-        <v>576</v>
+        <v>661</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>577</v>
-      </c>
-      <c r="B44" s="53" t="n">
-        <f aca="false">(4457+795)/1639</f>
-        <v>3.20439292251373</v>
+        <v>662</v>
+      </c>
+      <c r="B44" s="50" t="n">
+        <v>3</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>511</v>
+        <v>640</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>579</v>
-      </c>
-      <c r="B45" s="40" t="n">
-        <v>4</v>
+        <v>664</v>
+      </c>
+      <c r="B45" s="53" t="n">
+        <v>612</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>511</v>
+        <v>596</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>580</v>
+        <v>665</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="B46" s="34" t="n">
+        <v>666</v>
+      </c>
+      <c r="B46" s="53" t="n">
+        <v>164</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="B47" s="34" t="n">
         <f aca="false">2107/6227</f>
         <v>0.338365183876666</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>553</v>
-      </c>
-      <c r="D46" s="15" t="s">
+      <c r="C47" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="D47" s="15" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9" t="s">
-        <v>582</v>
-      </c>
-      <c r="B47" s="50" t="n">
-        <v>50</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>583</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>584</v>
-      </c>
-      <c r="B48" s="51" t="n">
+        <v>669</v>
+      </c>
+      <c r="B48" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="B49" s="51" t="n">
         <f aca="false">3080/2112</f>
         <v>1.45833333333333</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="B49" s="51" t="n">
+      <c r="C49" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="B50" s="51" t="n">
         <f aca="false">2584/2112</f>
         <v>1.22348484848485</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="D49" s="15" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="s">
-        <v>586</v>
-      </c>
-      <c r="B50" s="42" t="n">
-        <v>700</v>
-      </c>
       <c r="C50" s="8" t="s">
-        <v>587</v>
+        <v>643</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>588</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>589</v>
-      </c>
-      <c r="B51" s="52" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C51" s="8"/>
+        <v>673</v>
+      </c>
+      <c r="B51" s="42" t="n">
+        <v>700</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>674</v>
+      </c>
       <c r="D51" s="15" t="s">
-        <v>162</v>
+        <v>675</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
-        <v>590</v>
+        <v>676</v>
       </c>
       <c r="B52" s="52" t="n">
-        <v>0.18</v>
+        <v>0.04</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="15" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
-        <v>591</v>
+        <v>677</v>
       </c>
       <c r="B53" s="52" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="15" t="s">
-        <v>592</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
-        <v>593</v>
-      </c>
-      <c r="B54" s="48" t="n">
-        <v>7</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>594</v>
-      </c>
+        <v>678</v>
+      </c>
+      <c r="B54" s="52" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C54" s="8"/>
       <c r="D54" s="15" t="s">
-        <v>595</v>
+        <v>679</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="B55" s="52" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="C55" s="8"/>
+        <v>680</v>
+      </c>
+      <c r="B55" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>681</v>
+      </c>
       <c r="D55" s="15" t="s">
-        <v>597</v>
+        <v>682</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="B56" s="48" t="n">
-        <v>139829</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>599</v>
-      </c>
+        <v>683</v>
+      </c>
+      <c r="B56" s="52" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="C56" s="8"/>
       <c r="D56" s="15" t="s">
-        <v>85</v>
+        <v>684</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
-        <v>600</v>
-      </c>
-      <c r="B57" s="48" t="n">
-        <v>3224.24</v>
+        <v>685</v>
+      </c>
+      <c r="B57" s="50" t="n">
+        <v>44.99</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>599</v>
+        <v>640</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>93</v>
+        <v>686</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9" t="s">
-        <v>601</v>
+        <v>687</v>
       </c>
       <c r="B58" s="48" t="n">
-        <v>11237</v>
+        <v>139829</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>599</v>
+        <v>688</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>602</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9" t="s">
-        <v>603</v>
+        <v>689</v>
       </c>
       <c r="B59" s="48" t="n">
-        <v>4741.82</v>
+        <v>3224.24</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>599</v>
+        <v>688</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>604</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
-        <v>605</v>
+        <v>690</v>
       </c>
       <c r="B60" s="48" t="n">
-        <v>7096</v>
+        <v>11237</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>599</v>
+        <v>688</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>106</v>
+        <v>691</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="9" t="s">
-        <v>606</v>
+        <v>692</v>
       </c>
       <c r="B61" s="48" t="n">
-        <v>9000</v>
+        <v>4741.82</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>599</v>
+        <v>688</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>115</v>
+        <v>693</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9" t="s">
-        <v>607</v>
+        <v>694</v>
       </c>
       <c r="B62" s="48" t="n">
-        <v>717.75</v>
+        <v>7096</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>599</v>
+        <v>688</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="s">
-        <v>608</v>
+        <v>695</v>
       </c>
       <c r="B63" s="48" t="n">
-        <v>1090</v>
+        <v>9000</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>599</v>
+        <v>688</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="s">
-        <v>609</v>
+        <v>696</v>
       </c>
       <c r="B64" s="48" t="n">
+        <v>717.75</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="B65" s="48" t="n">
+        <v>1090</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="B66" s="48" t="n">
         <v>6672.64</v>
       </c>
-      <c r="C64" s="8" t="s">
-        <v>599</v>
-      </c>
-      <c r="D64" s="15" t="s">
+      <c r="C66" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="D66" s="15" t="s">
         <v>102</v>
       </c>
     </row>

--- a/antares/twin/docs/Кошторис_будівництва_під_ключ_СЕС_АБК_Антарес_ДБН_інвертор_Deye_100_кВт_28.10.2026.xlsx
+++ b/antares/twin/docs/Кошторис_будівництва_під_ключ_СЕС_АБК_Антарес_ДБН_інвертор_Deye_100_кВт_28.10.2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="725">
   <si>
     <t xml:space="preserve">Кошторис будівництва під ключ — СЕС на даху АБК, ТОВ МК «Антарес», варіант «ДБН»</t>
   </si>
@@ -298,10 +298,10 @@
     <t xml:space="preserve">4.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Кабель ВВГнг 5×70 мм², мідь — інвертор → щит СЕС біля вступного щита АБК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cable VVGng 5×70 mm² copper — inverter to PV board at the building main board</t>
+    <t xml:space="preserve">Провід СІП-4 4×70 мм² (Al, 0,6/1 кВ) — інвертор → лоток → підвіс через проїзд → щит СЕС у ТП-5913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIP-4 4×70 mm² (Al, 0.6/1 kV) — inverter → tray → overhead span across the driveway → PV board in TP-5913</t>
   </si>
   <si>
     <t xml:space="preserve">amperia.com.ua, 28.10.2026, у наявності</t>
@@ -310,10 +310,10 @@
     <t xml:space="preserve">4.4</t>
   </si>
   <si>
-    <t xml:space="preserve">Щит СЕС: автоматичний вимикач ABB A2B 250 TMF 200 (3P, 200 А) у корпусі IP54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PV board: MCCB ABB A2B 250 TMF 200 (3P, 200 A) in IP54 enclosure</t>
+    <t xml:space="preserve">Щит СЕС у ТП-5913: автоматичний вимикач ABB A2B 250 TMF 200 (3P, 200 А) у корпусі IP54, приєднання до РУ-0,4 кВ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PV board in TP-5913: MCCB ABB A2B 250 TMF 200 (3P, 200 A) in IP54 enclosure, connection to the 0.4 kV switchgear</t>
   </si>
   <si>
     <t xml:space="preserve">компл / set</t>
@@ -337,10 +337,10 @@
     <t xml:space="preserve">4.6</t>
   </si>
   <si>
-    <t xml:space="preserve">Лічильник CHINT DTSU666 з трансформаторами струму 250 А — обмеження видачі в мережу (Zero Export)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meter CHINT DTSU666 with 250 A CTs — export limiting (Zero Export)</t>
+    <t xml:space="preserve">Лічильник CHINT DTSU666 з трансформаторами струму 250 А на вводі АБК — інвертор видає не більше, ніж споживає АБК (Zero Export)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meter CHINT DTSU666 with 250 A CTs at the building input — inverter output limited to the building load (Zero Export)</t>
   </si>
   <si>
     <t xml:space="preserve">hotline.ua (Технопоставка), 28.10.2026</t>
@@ -433,6 +433,27 @@
     <t xml:space="preserve">кошторис СЕС і УЗЕ 26.10 / estimate 26.10</t>
   </si>
   <si>
+    <t xml:space="preserve">4.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Арматура підвісу СІП: затискачі анкерні ЗА 31 4×(25–70) — 2, гаки GHP 16М з дюбелями — 2, кронштейни фасадні SC 93-6PC — 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overhead span fittings: anchor clamps ZA 31 4×(25–70) — 2, wall hooks GHP 16M with plugs — 2, facade brackets SC 93-6PC — 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amperia.com.ua, 28.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Провід Cu 1×16 мм² ж-з — PE від інвертора уздовж СІП до ГЗШ ТП-5913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu wire 1×16 mm² green-yellow — PE from the inverter along the SIP to the TP-5913 earthing bar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Разом купуємо в Україні</t>
   </si>
   <si>
@@ -652,22 +673,22 @@
     <t xml:space="preserve">Strings: 11 × 12 modules, 2 per MPPT, the wall string on its own MPPT; Voc at −30 °C 676 V ≤ 1000 V. Full bill of materials — sheet «Специфікація», strings — sheet «Стрінги».</t>
   </si>
   <si>
-    <t xml:space="preserve">Інвертор — на північній стіні надбудови сходів над нижнім дахом (+10,6), у тіні; кабель AC — у надбудову і стояком сходів до щита СЕС біля вступного щита АБК. Струм інвертора до 159,4 А при 400 В, вимикач 200 А, кабель 5×70 мм² мідь.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inverter on the north wall of the stair house above the lower roof (+10.6), in shade; AC cable into the stair house and down the stair riser to the PV board next to the building main board. Inverter current up to 159.4 A at 400 V, 200 A breaker, 5×70 mm² copper cable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Блискавкозахист — без зовнішніх щогл (як том 7 СЕС цеху): вирівнювання потенціалів кріплення провідником Cu 1×6 у лотках, по 2 приєднання на блок кріплення, Cu 1×16 до PE інвертора і до прутка на парапеті в місці переходу лотка; ПЗІП тип II в інверторі, тип II у щиті СЕС, ПЗІП RS485.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightning protection without external masts (as volume 7 of the shop PV): bonding of the mounting with Cu 1×6 in trays, 2 connections per mounting block, Cu 1×16 to inverter PE and to the parapet rod where the tray crosses; type II SPD in the inverter and in the PV board, RS485 SPD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Робота без видачі в мережу: лічильник на вводі АБК і обмеження потужності інвертора (Zero Export); про генеруючу установку без видачі в мережу повідомляють ОСР за Додатком 11 до Кодексу систем розподілу.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operation without export: meter at the building input and inverter power limiting (Zero Export); the DSO is notified of a non-exporting generating unit per Annex 11 of the Distribution System Code.</t>
+    <t xml:space="preserve">Інвертор — на північній стіні надбудови сходів над нижнім дахом (+10,6), у тіні; провід СІП-4 4×70 — у лотку до західного парапету, з даху на підвісі через проїзд до ТП-5913 (проліт ≈8 м, анкерні затискачі на гаках), щит СЕС — у ТП-5913. Струм інвертора до 159,4 А при 400 В, вимикач 200 А.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inverter on the north wall of the stair house above the lower roof (+10.6), in shade; SIP-4 4×70 in the tray to the west parapet, then an overhead span across the driveway to TP-5913 (≈8 m, anchor clamps on hooks); the PV board is in TP-5913. Inverter current up to 159.4 A at 400 V, 200 A breaker.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Блискавкозахист — без зовнішніх щогл (як том 7 СЕС цеху): механічно зв'язані блоки кріплення з'єднані провідником Cu 1×6 у лотках, по 2 приєднання на блок; Cu 1×16 — до PE інвертора, до прутка на парапеті і уздовж СІП до головної заземлювальної шини ТП-5913; ПЗІП тип II в інверторі і в щиті СЕС, ПЗІП лінії RS485.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightning protection without external masts (as volume 7 of the shop PV): mechanically connected mounting blocks bonded with Cu 1×6 in trays, 2 connections per block; Cu 1×16 to the inverter PE, to the parapet rod and along the SIP to the TP-5913 main earthing bar; type II SPD in the inverter and in the PV board, RS485 SPD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Робота без видачі в мережу: лічильник на вводі АБК, інвертор видає не більше, ніж споживає АБК (Zero Export); про генеруючу установку без видачі в мережу повідомляють ОСР за Додатком 11 до Кодексу систем розподілу.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operation without export: meter at the building input, inverter output limited to the building load (Zero Export); the DSO is notified of a non-exporting generating unit per Annex 11 of the Distribution System Code.</t>
   </si>
   <si>
     <t xml:space="preserve">Не входить: обстеження будівлі й несучої здатності покрівлі (постанова КМУ № 406), проєктна документація, ремонт покрівлі; площадка з огорожею на арці (поз. 4.9) — за КП виробника драбини.</t>
@@ -1387,66 +1408,81 @@
     <t xml:space="preserve">G2</t>
   </si>
   <si>
-    <t xml:space="preserve">по стіні і стояку сходів, + 10 % / along wall and stair riser, + 10 %</t>
+    <t xml:space="preserve">Self-supporting insulated cable SIP-4 4×70 mm² (Al, 0.6/1 kV) — inverter → tray → overhead span across the driveway → PV board in TP-5913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">траса 26,1 м (проліт 8,1 м), + 10 % / route, span, + 10 %</t>
   </si>
   <si>
     <t xml:space="preserve">G3</t>
   </si>
   <si>
-    <t xml:space="preserve">Наконечник мідний луджений ТМЛ 70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tinned copper lug 70 mm²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 жил × 2 кінці / 5 cores × 2 ends</t>
+    <t xml:space="preserve">Арматура підвісу СІП: затискач анкерний ЗА 31 4×(25–70) — 2, гак GHP 16М з дюбелями — 2, кронштейн фасадний SC 93-6PC — 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overhead span fittings: anchor clamp ZA 31 4×(25–70) — 2, wall hook GHP 16M with plugs — 2, facade bracket SC 93-6PC — 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">стіна АБК і стіна ТП-5913 / building wall and TP-5913 wall</t>
   </si>
   <si>
     <t xml:space="preserve">G4</t>
   </si>
   <si>
+    <t xml:space="preserve">Наконечник алюмінієво-мідний DTL-2-70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aluminium-copper lug DTL-2-70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 жили × 2 кінці / 4 cores × 2 ends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Автоматичний вимикач ABB FormulA A2B 250 TMF 200, 3P, 200 А</t>
   </si>
   <si>
     <t xml:space="preserve">Moulded-case breaker ABB FormulA A2B 250 TMF 200, 3P, 200 A</t>
   </si>
   <si>
-    <t xml:space="preserve">струм інвертора до 159,4 А / inverter current up to 159.4 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Корпус щита IEK ЩМП-4.6.2-0 74 У2, 400 × 600 × 250, IP54 — щит СЕС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enclosure IEK ShchMP-4.6.2-0, 400 × 600 × 250, IP54 — PV board</t>
+    <t xml:space="preserve">струм інвертора до 159,4 А; щит СЕС — у ТП-5913, приєднання до РУ-0,4 кВ / inverter current up to 159.4 A; PV board in TP-5913</t>
   </si>
   <si>
     <t xml:space="preserve">G6</t>
   </si>
   <si>
-    <t xml:space="preserve">ПЗІП AC тип 2, 4P, 280 В (Eaton SPCT2-280/4) — у щиті СЕС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC surge protector type 2, 4P, 280 V (Eaton SPCT2-280/4) — in PV board</t>
-  </si>
-  <si>
-    <t xml:space="preserve">вхід AC у будівлю / AC entry into the building</t>
+    <t xml:space="preserve">Корпус щита IEK ЩМП-4.6.2-0 74 У2, 400 × 600 × 250, IP54 — щит СЕС у ТП-5913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enclosure IEK ShchMP-4.6.2-0, 400 × 600 × 250, IP54 — PV board in TP-5913</t>
   </si>
   <si>
     <t xml:space="preserve">G7</t>
   </si>
   <si>
-    <t xml:space="preserve">Лічильник CHINT DTSU666 з трансформаторами струму 250 А — на вводі АБК, обмеження видачі в мережу (Zero Export)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meter CHINT DTSU666 with 250 A current transformers — at the building input, export limiting (Zero Export)</t>
+    <t xml:space="preserve">ПЗІП AC тип 2, 4P, 280 В (Eaton SPCT2-280/4) — у щиті СЕС у ТП-5913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC surge protector type 2, 4P, 280 V (Eaton SPCT2-280/4) — in PV board in TP-5913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">на вводі лінії СІП у ТП / at the overhead line entry into the TP</t>
   </si>
   <si>
     <t xml:space="preserve">G8</t>
   </si>
   <si>
+    <t xml:space="preserve">Лічильник CHINT DTSU666 з трансформаторами струму 250 А — на вводі АБК: інвертор видає не більше, ніж споживає АБК (Zero Export)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meter CHINT DTSU666 with 250 A current transformers — at the building input: inverter output limited to the building load (Zero Export)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G9</t>
+  </si>
+  <si>
     <t xml:space="preserve">Кабель RS485 2×2×0,75 мм² в екрані — лічильник → інвертор</t>
   </si>
   <si>
@@ -1456,13 +1492,13 @@
     <t xml:space="preserve">уздовж кабелю AC / along AC cable</t>
   </si>
   <si>
-    <t xml:space="preserve">G9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Прохід кабелів крізь стіну надбудови з ущільненням</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cable wall pass-through into the stair house with sealing</t>
+    <t xml:space="preserve">G10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прохід крізь стіну з ущільненням: у ТП-5913 (СІП і PE) і в надбудову (RS485)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wall pass-through with sealing: into TP-5913 (SIP and PE) and into the stair house (RS485)</t>
   </si>
   <si>
     <t xml:space="preserve">H. Блискавкозахист і вирівнювання потенціалів</t>
@@ -1480,7 +1516,7 @@
     <t xml:space="preserve">Cu wire 1×6 mm² green-yellow — equipotential bonding in trays and branches to mounting</t>
   </si>
   <si>
-    <t xml:space="preserve">лотки 106,3 м + 10 % і 28 відгалужень / trays + 10 % and 28 branches</t>
+    <t xml:space="preserve">лотки 106,3 м + 10 % і 28 відгалужень до 14 механічно зв'язаних блоків / trays + 10 % and branches to bonded blocks</t>
   </si>
   <si>
     <t xml:space="preserve">H2</t>
@@ -1495,6 +1531,18 @@
     <t xml:space="preserve">H3</t>
   </si>
   <si>
+    <t xml:space="preserve">Провід Cu 1×16 мм² жовто-зелений — PE від інвертора уздовж СІП до головної заземлювальної шини ТП-5913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu wire 1×16 mm² green-yellow — PE from the inverter along the SIP to the main earthing bar of TP-5913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">траса 27,6 м + 10 %; на прольоті — стяжками до СІП / route + 10 %; tied to the SIP on the span</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Затискач до профілю і відгалужувальний EN 62561-1</t>
   </si>
   <si>
@@ -1504,7 +1552,7 @@
     <t xml:space="preserve">по 2 на 14 блоків кріплення + 4 / 2 per mounting block + 4</t>
   </si>
   <si>
-    <t xml:space="preserve">H4</t>
+    <t xml:space="preserve">H5</t>
   </si>
   <si>
     <t xml:space="preserve">Шайба контактна зубчаста під болти гільз</t>
@@ -1516,7 +1564,7 @@
     <t xml:space="preserve">як болти M10×60 гільз / as sleeve bolts M10×60</t>
   </si>
   <si>
-    <t xml:space="preserve">H5</t>
+    <t xml:space="preserve">H6</t>
   </si>
   <si>
     <t xml:space="preserve">Наконечник 16 мм² і контрольне з'єднання</t>
@@ -1525,7 +1573,10 @@
     <t xml:space="preserve">Lug 16 mm² and test joint</t>
   </si>
   <si>
-    <t xml:space="preserve">H6</t>
+    <t xml:space="preserve">прут на парапеті, PE інвертора, ГЗШ ТП-5913 / parapet rod, inverter PE, TP-5913 earthing bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H7</t>
   </si>
   <si>
     <t xml:space="preserve">ПЗІП лінії RS485</t>
@@ -1876,12 +1927,15 @@
     <t xml:space="preserve">кріплення модулів — 3D-модель (кожен блок), опори лотків / module mounting — 3D model (every block), tray supports</t>
   </si>
   <si>
-    <t xml:space="preserve">Кабель AC інвертор → щит СЕС / AC cable inverter → PV board</t>
+    <t xml:space="preserve">Провід СІП-4 4×70: інвертор → ТП-5913 / SIP-4 4×70: inverter → TP-5913</t>
   </si>
   <si>
     <t xml:space="preserve">м</t>
   </si>
   <si>
+    <t xml:space="preserve">траса з 3D-моделі: лоток, підвіс через проїзд, стіна ТП, + 10 % / route from the 3D model, + 10 %</t>
+  </si>
+  <si>
     <t xml:space="preserve">Кабель RS485 лічильник → інвертор / RS485 cable meter → inverter</t>
   </si>
   <si>
@@ -1918,6 +1972,12 @@
     <t xml:space="preserve">ланцюжок тяг лінії не переходить гребінь — анкер на верхній лазі (правило КМ даху цеху) / tie chain not crossing the ridge</t>
   </si>
   <si>
+    <t xml:space="preserve">Провід PE Cu 1×16 до ГЗШ ТП-5913 / PE Cu 1×16 to TP-5913 earthing bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">уздовж СІП, + 10 % / along the SIP, + 10 %</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ставки і ціни / Rates and prices</t>
   </si>
   <si>
@@ -2080,6 +2140,12 @@
     <t xml:space="preserve">паспорт Deye SUN-70~110K-G03 (deye.com): Euro 98,2 %, макс. 98,8 %</t>
   </si>
   <si>
+    <t xml:space="preserve">Провід Cu 1×16 мм² ж-з, Україна / Cu wire 1×16 mm² green-yellow, Ukraine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">кошторис СЕС і УЗЕ 26.10, позиція «Провід Cu 1×16 мм² ж-з» / estimate 26.10</t>
+  </si>
+  <si>
     <t xml:space="preserve">Анкер від сповзання з герметизацією, Україна / Anti-slide anchor with sealing, Ukraine</t>
   </si>
   <si>
@@ -2120,6 +2186,18 @@
   </si>
   <si>
     <t xml:space="preserve">ПЗІП AC тип 2 Eaton SPCT2-280/4, 4P, 280 В</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Провід СІП-4 4×70 (Al, ДСТУ), за 1 м</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Затискач анкерний ЗА 31 4×(25–70) NIGAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гак для плоских поверхонь GHP 16М з дюбелями (SICAME)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фасадний кронштейн SC 93-6PC d 20–50 (SICAME)</t>
   </si>
 </sst>
 </file>
@@ -2796,7 +2874,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.51"/>
@@ -2887,7 +2965,7 @@
         <v>135</v>
       </c>
       <c r="F7" s="12" t="n">
-        <f aca="false">Параметри!$B$31</f>
+        <f aca="false">Параметри!$B$32</f>
         <v>73</v>
       </c>
       <c r="G7" s="13" t="n">
@@ -2919,7 +2997,7 @@
         <v>86</v>
       </c>
       <c r="F8" s="12" t="n">
-        <f aca="false">Параметри!$B$32</f>
+        <f aca="false">Параметри!$B$33</f>
         <v>11.1688311688312</v>
       </c>
       <c r="G8" s="13" t="n">
@@ -2951,7 +3029,7 @@
         <v>37</v>
       </c>
       <c r="F9" s="12" t="n">
-        <f aca="false">Параметри!$B$33</f>
+        <f aca="false">Параметри!$B$34</f>
         <v>10.897619047619</v>
       </c>
       <c r="G9" s="13" t="n">
@@ -2983,7 +3061,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="12" t="n">
-        <f aca="false">Параметри!$B$34</f>
+        <f aca="false">Параметри!$B$35</f>
         <v>8.6026936026936</v>
       </c>
       <c r="G10" s="13" t="n">
@@ -3015,7 +3093,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="12" t="n">
-        <f aca="false">Параметри!$B$35</f>
+        <f aca="false">Параметри!$B$36</f>
         <v>60</v>
       </c>
       <c r="G11" s="13" t="n">
@@ -3047,7 +3125,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="12" t="n">
-        <f aca="false">Параметри!$B$36</f>
+        <f aca="false">Параметри!$B$37</f>
         <v>64.5729166666667</v>
       </c>
       <c r="G12" s="13" t="n">
@@ -3079,7 +3157,7 @@
         <v>132</v>
       </c>
       <c r="F13" s="12" t="n">
-        <f aca="false">Параметри!$B$37</f>
+        <f aca="false">Параметри!$B$38</f>
         <v>1.13636363636364</v>
       </c>
       <c r="G13" s="13" t="n">
@@ -3111,7 +3189,7 @@
         <v>55</v>
       </c>
       <c r="F14" s="16" t="n">
-        <f aca="false">Параметри!$B$38</f>
+        <f aca="false">Параметри!$B$39</f>
         <v>0.262857142857143</v>
       </c>
       <c r="G14" s="13" t="n">
@@ -3171,7 +3249,7 @@
       <c r="D17" s="8"/>
       <c r="E17" s="21"/>
       <c r="F17" s="22" t="n">
-        <f aca="false">Параметри!$B$39</f>
+        <f aca="false">Параметри!$B$40</f>
         <v>0.05</v>
       </c>
       <c r="G17" s="13"/>
@@ -3234,7 +3312,7 @@
         <v>135</v>
       </c>
       <c r="F20" s="12" t="n">
-        <f aca="false">Параметри!$B$40</f>
+        <f aca="false">Параметри!$B$41</f>
         <v>11.7845117845118</v>
       </c>
       <c r="G20" s="13"/>
@@ -3264,7 +3342,7 @@
         <v>132</v>
       </c>
       <c r="F21" s="12" t="n">
-        <f aca="false">Параметри!$B$41</f>
+        <f aca="false">Параметри!$B$42</f>
         <v>6.62878787878788</v>
       </c>
       <c r="G21" s="13"/>
@@ -3289,7 +3367,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="21"/>
       <c r="F22" s="22" t="n">
-        <f aca="false">Параметри!$B$42</f>
+        <f aca="false">Параметри!$B$43</f>
         <v>0.003</v>
       </c>
       <c r="G22" s="13"/>
@@ -3314,7 +3392,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="21"/>
       <c r="F23" s="23" t="n">
-        <f aca="false">Параметри!$B$43</f>
+        <f aca="false">Параметри!$B$44</f>
         <v>1.14313318257672</v>
       </c>
       <c r="G23" s="13"/>
@@ -3376,7 +3454,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="12" t="n">
-        <f aca="false">Параметри!$B$58/(1+Параметри!$B$54)/Параметри!$B$29</f>
+        <f aca="false">Параметри!$B$60/(1+Параметри!$B$55)/Параметри!$B$30</f>
         <v>2595.77114427861</v>
       </c>
       <c r="G26" s="13"/>
@@ -3406,7 +3484,7 @@
         <v>684</v>
       </c>
       <c r="F27" s="12" t="n">
-        <f aca="false">Параметри!$B$44</f>
+        <f aca="false">Параметри!$B$45</f>
         <v>3</v>
       </c>
       <c r="G27" s="13"/>
@@ -3433,16 +3511,16 @@
       </c>
       <c r="E28" s="11" t="n">
         <f aca="false">Параметри!B17</f>
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F28" s="12" t="n">
-        <f aca="false">Параметри!$B$59/(1+Параметри!$B$54)/Параметри!$B$29</f>
-        <v>59.8544590480434</v>
+        <f aca="false">Параметри!$B$69/(1+Параметри!$B$55)/Параметри!$B$30</f>
+        <v>5.08149550753694</v>
       </c>
       <c r="G28" s="13"/>
       <c r="H28" s="14" t="n">
         <f aca="false">E28*F28</f>
-        <v>2693.45065716195</v>
+        <v>147.363369718571</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>93</v>
@@ -3465,7 +3543,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="12" t="n">
-        <f aca="false">Параметри!$B$60/(1+Параметри!$B$54)/Параметри!$B$29+Параметри!$B$61/(1+Параметри!$B$54)/Параметри!$B$29</f>
+        <f aca="false">Параметри!$B$62/(1+Параметри!$B$55)/Параметри!$B$30+Параметри!$B$63/(1+Параметри!$B$55)/Параметри!$B$30</f>
         <v>296.629167594862</v>
       </c>
       <c r="G29" s="13"/>
@@ -3494,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="12" t="n">
-        <f aca="false">Параметри!$B$66/(1+Параметри!$B$54)/Параметри!$B$29</f>
+        <f aca="false">Параметри!$B$68/(1+Параметри!$B$55)/Параметри!$B$30</f>
         <v>123.870201232643</v>
       </c>
       <c r="G30" s="13"/>
@@ -3506,7 +3584,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
         <v>103</v>
       </c>
@@ -3523,7 +3601,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="12" t="n">
-        <f aca="false">Параметри!$B$62/(1+Параметри!$B$54)/Параметри!$B$29</f>
+        <f aca="false">Параметри!$B$64/(1+Параметри!$B$55)/Параметри!$B$30</f>
         <v>131.729412638301</v>
       </c>
       <c r="G31" s="13"/>
@@ -3553,7 +3631,7 @@
         <v>684</v>
       </c>
       <c r="F32" s="12" t="n">
-        <f aca="false">Параметри!$B$47</f>
+        <f aca="false">Параметри!$B$48</f>
         <v>0.338365183876666</v>
       </c>
       <c r="G32" s="13"/>
@@ -3583,7 +3661,7 @@
         <v>5.8</v>
       </c>
       <c r="F33" s="12" t="n">
-        <f aca="false">Параметри!$B$63/(1+Параметри!$B$54)/Параметри!$B$29</f>
+        <f aca="false">Параметри!$B$65/(1+Параметри!$B$55)/Параметри!$B$30</f>
         <v>167.075072399198</v>
       </c>
       <c r="G33" s="13"/>
@@ -3642,7 +3720,7 @@
         <v>5.6</v>
       </c>
       <c r="F35" s="12" t="n">
-        <f aca="false">Параметри!$B$63/(1+Параметри!$B$54)/Параметри!$B$29</f>
+        <f aca="false">Параметри!$B$65/(1+Параметри!$B$55)/Параметри!$B$30</f>
         <v>167.075072399198</v>
       </c>
       <c r="G35" s="13"/>
@@ -3672,7 +3750,7 @@
         <v>99</v>
       </c>
       <c r="F36" s="12" t="n">
-        <f aca="false">Параметри!$B$64/(1+Параметри!$B$54)/Параметри!$B$29</f>
+        <f aca="false">Параметри!$B$66/(1+Параметри!$B$55)/Параметри!$B$30</f>
         <v>13.324237023836</v>
       </c>
       <c r="G36" s="13"/>
@@ -3702,7 +3780,7 @@
         <v>63</v>
       </c>
       <c r="F37" s="12" t="n">
-        <f aca="false">Параметри!$B$65/(1+Параметри!$B$54)/Параметри!$B$29</f>
+        <f aca="false">Параметри!$B$67/(1+Параметри!$B$55)/Параметри!$B$30</f>
         <v>20.2346476572362</v>
       </c>
       <c r="G37" s="13"/>
@@ -3732,7 +3810,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="12" t="n">
-        <f aca="false">Параметри!$B$57</f>
+        <f aca="false">Параметри!$B$59</f>
         <v>44.99</v>
       </c>
       <c r="G38" s="13"/>
@@ -3744,588 +3822,623 @@
         <v>135</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="17"/>
-      <c r="B39" s="18" t="s">
+    <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="B39" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="20" t="n">
-        <f aca="false">SUM(H26:H38)</f>
-        <v>13073.3304617945</v>
-      </c>
-      <c r="I39" s="17"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
+      <c r="C39" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="7" t="s">
+      <c r="D39" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <f aca="false">2*Параметри!$B$70/(1+Параметри!$B$55)/Параметри!$B$30+2*Параметри!$B$71/(1+Параметри!$B$55)/Параметри!$B$30+4*Параметри!$B$72/(1+Параметри!$B$55)/Параметри!$B$30</f>
+        <v>25.219425261751</v>
+      </c>
+      <c r="G39" s="13"/>
+      <c r="H39" s="14" t="n">
+        <f aca="false">E39*F39</f>
+        <v>25.219425261751</v>
+      </c>
+      <c r="I39" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-    </row>
-    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
+    </row>
+    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B40" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C40" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D40" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <f aca="false">Параметри!B26</f>
+        <v>31</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <f aca="false">Параметри!$B$58</f>
+        <v>3.17</v>
+      </c>
+      <c r="G40" s="13"/>
+      <c r="H40" s="14" t="n">
+        <f aca="false">E40*F40</f>
+        <v>98.27</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17"/>
+      <c r="B41" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="C41" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="20" t="n">
+        <f aca="false">SUM(H26:H40)</f>
+        <v>10650.7325996129</v>
+      </c>
+      <c r="I41" s="17"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E43" s="11" t="n">
         <f aca="false">Параметри!B11</f>
         <v>96.36</v>
       </c>
-      <c r="F41" s="12" t="n">
-        <f aca="false">Параметри!$B$48</f>
+      <c r="F43" s="12" t="n">
+        <f aca="false">Параметри!$B$49</f>
         <v>50</v>
-      </c>
-      <c r="G41" s="13"/>
-      <c r="H41" s="14" t="n">
-        <f aca="false">E41*F41</f>
-        <v>4818</v>
-      </c>
-      <c r="I41" s="15" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E42" s="11" t="n">
-        <f aca="false">Параметри!B9</f>
-        <v>132</v>
-      </c>
-      <c r="F42" s="12" t="n">
-        <f aca="false">Параметри!$B$49</f>
-        <v>1.45833333333333</v>
-      </c>
-      <c r="G42" s="13"/>
-      <c r="H42" s="14" t="n">
-        <f aca="false">E42*F42</f>
-        <v>192.5</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E43" s="11" t="n">
-        <f aca="false">Параметри!B9</f>
-        <v>132</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <f aca="false">Параметри!$B$50</f>
-        <v>1.22348484848485</v>
       </c>
       <c r="G43" s="13"/>
       <c r="H43" s="14" t="n">
         <f aca="false">E43*F43</f>
-        <v>161.5</v>
+        <v>4818</v>
       </c>
       <c r="I43" s="15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
+      <c r="B44" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="C44" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="D44" s="8" t="s">
-        <v>155</v>
+        <v>22</v>
       </c>
       <c r="E44" s="11" t="n">
-        <f aca="false">Параметри!B24</f>
-        <v>112</v>
+        <f aca="false">Параметри!B9</f>
+        <v>132</v>
       </c>
       <c r="F44" s="12" t="n">
-        <f aca="false">Параметри!$B$51/Параметри!$B$29</f>
-        <v>15.5936734239252</v>
+        <f aca="false">Параметри!$B$50</f>
+        <v>1.45833333333333</v>
       </c>
       <c r="G44" s="13"/>
       <c r="H44" s="14" t="n">
         <f aca="false">E44*F44</f>
+        <v>192.5</v>
+      </c>
+      <c r="I44" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <f aca="false">Параметри!B9</f>
+        <v>132</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <f aca="false">Параметри!$B$51</f>
+        <v>1.22348484848485</v>
+      </c>
+      <c r="G45" s="13"/>
+      <c r="H45" s="14" t="n">
+        <f aca="false">E45*F45</f>
+        <v>161.5</v>
+      </c>
+      <c r="I45" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <f aca="false">Параметри!B24</f>
+        <v>112</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <f aca="false">Параметри!$B$52/Параметри!$B$30</f>
+        <v>15.5936734239252</v>
+      </c>
+      <c r="G46" s="13"/>
+      <c r="H46" s="14" t="n">
+        <f aca="false">E46*F46</f>
         <v>1746.49142347962</v>
       </c>
-      <c r="I44" s="15" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="17"/>
-      <c r="B45" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="20" t="n">
-        <f aca="false">SUM(H41:H44)</f>
+      <c r="I46" s="15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="17"/>
+      <c r="B47" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="20" t="n">
+        <f aca="false">SUM(H43:H46)</f>
         <v>6918.49142347962</v>
       </c>
-      <c r="I45" s="17"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="26"/>
-      <c r="B47" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="C47" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="29" t="n">
-        <f aca="false">H15+H18+H24+H39+H45</f>
-        <v>36013.8862419466</v>
-      </c>
-      <c r="I47" s="26"/>
+      <c r="I47" s="17"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="D50" s="8"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="22" t="n">
-        <f aca="false">Параметри!$B$52</f>
+      <c r="A49" s="26"/>
+      <c r="B49" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="29" t="n">
+        <f aca="false">H15+H18+H24+H41+H47</f>
+        <v>33591.288379765</v>
+      </c>
+      <c r="I49" s="26"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B51" s="6"/>
+      <c r="C51" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" s="8"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="22" t="n">
+        <f aca="false">Параметри!$B$53</f>
         <v>0.04</v>
       </c>
-      <c r="G50" s="13"/>
-      <c r="H50" s="14" t="n">
-        <f aca="false">H47*F50</f>
-        <v>1440.55544967787</v>
-      </c>
-      <c r="I50" s="15" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="22" t="n">
-        <f aca="false">Параметри!$B$53</f>
+      <c r="G52" s="13"/>
+      <c r="H52" s="14" t="n">
+        <f aca="false">H49*F52</f>
+        <v>1343.6515351906</v>
+      </c>
+      <c r="I52" s="15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="D53" s="8"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="22" t="n">
+        <f aca="false">Параметри!$B$54</f>
         <v>0.18</v>
       </c>
-      <c r="G51" s="13"/>
-      <c r="H51" s="14" t="n">
-        <f aca="false">H47*F51</f>
-        <v>6482.49952355039</v>
-      </c>
-      <c r="I51" s="15" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="17"/>
-      <c r="B52" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="20" t="n">
-        <f aca="false">H50+H51</f>
-        <v>7923.05497322826</v>
-      </c>
-      <c r="I52" s="17"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="14" t="n">
+        <f aca="false">H49*F53</f>
+        <v>6046.4319083577</v>
+      </c>
+      <c r="I53" s="15" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="26"/>
-      <c r="B54" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="C54" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="29" t="n">
-        <f aca="false">H47+H52</f>
-        <v>43936.9412151749</v>
-      </c>
-      <c r="I54" s="26"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="17"/>
-      <c r="B55" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="20" t="n">
-        <f aca="false">H54*Параметри!$B$54</f>
-        <v>8787.38824303498</v>
-      </c>
-      <c r="I55" s="17"/>
+      <c r="A54" s="17"/>
+      <c r="B54" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="20" t="n">
+        <f aca="false">H52+H53</f>
+        <v>7390.0834435483</v>
+      </c>
+      <c r="I54" s="17"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="26"/>
       <c r="B56" s="27" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C56" s="28" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D56" s="26"/>
       <c r="E56" s="26"/>
       <c r="F56" s="26"/>
       <c r="G56" s="26"/>
       <c r="H56" s="29" t="n">
-        <f aca="false">H54+H55</f>
-        <v>52724.3294582099</v>
+        <f aca="false">H49+H54</f>
+        <v>40981.3718233133</v>
       </c>
       <c r="I56" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="17"/>
-      <c r="B58" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="20" t="n">
-        <f aca="false">(H54-H7)*Параметри!$B$54</f>
-        <v>6816.38824303498</v>
-      </c>
-      <c r="I58" s="17"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="26"/>
-      <c r="B59" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C59" s="28" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="17"/>
+      <c r="B57" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="D59" s="26"/>
-      <c r="E59" s="26"/>
-      <c r="F59" s="26"/>
-      <c r="G59" s="26"/>
-      <c r="H59" s="29" t="n">
-        <f aca="false">H54+H58</f>
-        <v>50753.3294582099</v>
-      </c>
-      <c r="I59" s="26"/>
+      <c r="C57" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="20" t="n">
+        <f aca="false">H56*Параметри!$B$55</f>
+        <v>8196.27436466266</v>
+      </c>
+      <c r="I57" s="17"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="26"/>
+      <c r="B58" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="29" t="n">
+        <f aca="false">H56+H57</f>
+        <v>49177.6461879759</v>
+      </c>
+      <c r="I58" s="26"/>
+    </row>
+    <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="17"/>
+      <c r="B60" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="20" t="n">
+        <f aca="false">(H56-H7)*Параметри!$B$55</f>
+        <v>6225.27436466266</v>
+      </c>
+      <c r="I60" s="17"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="17"/>
-      <c r="B61" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="D61" s="17"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="20" t="n">
-        <f aca="false">H54/Параметри!B11</f>
-        <v>455.966596255447</v>
-      </c>
-      <c r="I61" s="17"/>
+      <c r="A61" s="26"/>
+      <c r="B61" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="29" t="n">
+        <f aca="false">H56+H60</f>
+        <v>47206.6461879759</v>
+      </c>
+      <c r="I61" s="26"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B63" s="6"/>
-      <c r="C63" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="17"/>
-      <c r="B64" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="C64" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E64" s="17"/>
-      <c r="F64" s="17"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="31" t="n">
-        <f aca="false">Параметри!B11</f>
-        <v>96.36</v>
-      </c>
-      <c r="I64" s="17"/>
+      <c r="A63" s="17"/>
+      <c r="B63" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="20" t="n">
+        <f aca="false">H56/Параметри!B11</f>
+        <v>425.294435692334</v>
+      </c>
+      <c r="I63" s="17"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="17"/>
-      <c r="B65" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="C65" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="E65" s="17"/>
-      <c r="F65" s="17"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="32" t="n">
-        <f aca="false">Параметри!B14</f>
-        <v>87.1</v>
-      </c>
-      <c r="I65" s="17"/>
+      <c r="A65" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B65" s="6"/>
+      <c r="C65" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="17"/>
       <c r="B66" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C66" s="30" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
       <c r="G66" s="17"/>
-      <c r="H66" s="32" t="n">
-        <f aca="false">H65*Параметри!$B$56</f>
-        <v>85.5322</v>
+      <c r="H66" s="31" t="n">
+        <f aca="false">Параметри!B11</f>
+        <v>96.36</v>
       </c>
       <c r="I66" s="17"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="17"/>
       <c r="B67" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E67" s="17"/>
       <c r="F67" s="17"/>
       <c r="G67" s="17"/>
-      <c r="H67" s="33" t="n">
-        <f aca="false">H66*1000/H64</f>
-        <v>887.631797426318</v>
+      <c r="H67" s="32" t="n">
+        <f aca="false">Параметри!B14</f>
+        <v>87.1</v>
       </c>
       <c r="I67" s="17"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="17"/>
       <c r="B68" s="8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C68" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D68" s="8" t="s">
         <v>197</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>198</v>
       </c>
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="17"/>
-      <c r="H68" s="34" t="n">
-        <f aca="false">Параметри!$B$55/(1+Параметри!$B$54)/Параметри!$B$29</f>
-        <v>0.12994727853271</v>
+      <c r="H68" s="32" t="n">
+        <f aca="false">H67*Параметри!$B$57</f>
+        <v>85.5322</v>
       </c>
       <c r="I68" s="17"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="17"/>
       <c r="B69" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
       <c r="G69" s="17"/>
-      <c r="H69" s="14" t="n">
-        <f aca="false">H66*1000*H68</f>
-        <v>11114.6766169154</v>
+      <c r="H69" s="33" t="n">
+        <f aca="false">H68*1000/H66</f>
+        <v>887.631797426318</v>
       </c>
       <c r="I69" s="17"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="17"/>
       <c r="B70" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E70" s="17"/>
       <c r="F70" s="17"/>
       <c r="G70" s="17"/>
-      <c r="H70" s="35" t="n">
-        <f aca="false">H54/H69</f>
-        <v>3.95305619133419</v>
+      <c r="H70" s="34" t="n">
+        <f aca="false">Параметри!$B$56/(1+Параметри!$B$55)/Параметри!$B$30</f>
+        <v>0.12994727853271</v>
       </c>
       <c r="I70" s="17"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="17"/>
       <c r="B71" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E71" s="17"/>
       <c r="F71" s="17"/>
       <c r="G71" s="17"/>
       <c r="H71" s="14" t="n">
-        <f aca="false">H54/H66</f>
-        <v>513.688893950756</v>
+        <f aca="false">H68*1000*H70</f>
+        <v>11114.6766169154</v>
       </c>
       <c r="I71" s="17"/>
     </row>
-    <row r="73" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B73" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="C73" s="36"/>
-      <c r="D73" s="36"/>
-      <c r="E73" s="36"/>
-      <c r="F73" s="36"/>
-      <c r="G73" s="36"/>
-      <c r="H73" s="36"/>
-      <c r="I73" s="36"/>
-    </row>
-    <row r="74" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B74" s="37" t="s">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="17"/>
+      <c r="B72" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C72" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="E72" s="17"/>
+      <c r="F72" s="17"/>
+      <c r="G72" s="17"/>
+      <c r="H72" s="35" t="n">
+        <f aca="false">H56/H71</f>
+        <v>3.6871402772928</v>
+      </c>
+      <c r="I72" s="17"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="17"/>
+      <c r="B73" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C73" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="D73" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C74" s="37"/>
-      <c r="D74" s="37"/>
-      <c r="E74" s="37"/>
-      <c r="F74" s="37"/>
-      <c r="G74" s="37"/>
-      <c r="H74" s="37"/>
-      <c r="I74" s="37"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="17"/>
+      <c r="G73" s="17"/>
+      <c r="H73" s="14" t="n">
+        <f aca="false">H56/H68</f>
+        <v>479.133844602539</v>
+      </c>
+      <c r="I73" s="17"/>
     </row>
     <row r="75" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="36" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C75" s="36"/>
       <c r="D75" s="36"/>
@@ -4337,7 +4450,7 @@
     </row>
     <row r="76" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="37" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C76" s="37"/>
       <c r="D76" s="37"/>
@@ -4349,7 +4462,7 @@
     </row>
     <row r="77" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="36" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C77" s="36"/>
       <c r="D77" s="36"/>
@@ -4361,7 +4474,7 @@
     </row>
     <row r="78" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="37" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C78" s="37"/>
       <c r="D78" s="37"/>
@@ -4373,7 +4486,7 @@
     </row>
     <row r="79" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="36" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C79" s="36"/>
       <c r="D79" s="36"/>
@@ -4385,7 +4498,7 @@
     </row>
     <row r="80" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="37" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C80" s="37"/>
       <c r="D80" s="37"/>
@@ -4397,7 +4510,7 @@
     </row>
     <row r="81" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="36" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C81" s="36"/>
       <c r="D81" s="36"/>
@@ -4409,7 +4522,7 @@
     </row>
     <row r="82" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="37" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C82" s="37"/>
       <c r="D82" s="37"/>
@@ -4419,10 +4532,32 @@
       <c r="H82" s="37"/>
       <c r="I82" s="37"/>
     </row>
+    <row r="83" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B83" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="C83" s="36"/>
+      <c r="D83" s="36"/>
+      <c r="E83" s="36"/>
+      <c r="F83" s="36"/>
+      <c r="G83" s="36"/>
+      <c r="H83" s="36"/>
+      <c r="I83" s="36"/>
+    </row>
+    <row r="84" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B84" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="C84" s="37"/>
+      <c r="D84" s="37"/>
+      <c r="E84" s="37"/>
+      <c r="F84" s="37"/>
+      <c r="G84" s="37"/>
+      <c r="H84" s="37"/>
+      <c r="I84" s="37"/>
+    </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B73:I73"/>
-    <mergeCell ref="B74:I74"/>
     <mergeCell ref="B75:I75"/>
     <mergeCell ref="B76:I76"/>
     <mergeCell ref="B77:I77"/>
@@ -4431,6 +4566,8 @@
     <mergeCell ref="B80:I80"/>
     <mergeCell ref="B81:I81"/>
     <mergeCell ref="B82:I82"/>
+    <mergeCell ref="B83:I83"/>
+    <mergeCell ref="B84:I84"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4447,7 +4584,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -4461,12 +4598,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4486,19 +4623,19 @@
         <v>7</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="7" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -4507,13 +4644,13 @@
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>17</v>
@@ -4525,16 +4662,16 @@
         <v>14</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="7" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -4543,13 +4680,13 @@
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>17</v>
@@ -4561,18 +4698,18 @@
         <v>19</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>17</v>
@@ -4584,18 +4721,18 @@
         <v>19</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>17</v>
@@ -4607,18 +4744,18 @@
         <v>19</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>97</v>
@@ -4630,18 +4767,18 @@
         <v>19</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>17</v>
@@ -4653,18 +4790,18 @@
         <v>19</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>17</v>
@@ -4676,18 +4813,18 @@
         <v>19</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>17</v>
@@ -4699,18 +4836,18 @@
         <v>19</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>17</v>
@@ -4722,18 +4859,18 @@
         <v>19</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>17</v>
@@ -4745,18 +4882,18 @@
         <v>19</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>97</v>
@@ -4768,18 +4905,18 @@
         <v>19</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>97</v>
@@ -4791,18 +4928,18 @@
         <v>19</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D19" s="17" t="s">
         <v>17</v>
@@ -4814,18 +4951,18 @@
         <v>19</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>17</v>
@@ -4837,18 +4974,18 @@
         <v>19</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>97</v>
@@ -4860,18 +4997,18 @@
         <v>19</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D22" s="17" t="s">
         <v>17</v>
@@ -4883,16 +5020,16 @@
         <v>132</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="7" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -4901,13 +5038,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>17</v>
@@ -4919,18 +5056,18 @@
         <v>24</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="D25" s="17" t="s">
         <v>17</v>
@@ -4942,18 +5079,18 @@
         <v>24</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>17</v>
@@ -4965,18 +5102,18 @@
         <v>24</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>17</v>
@@ -4988,18 +5125,18 @@
         <v>24</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D28" s="17" t="s">
         <v>97</v>
@@ -5011,18 +5148,18 @@
         <v>24</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D29" s="17" t="s">
         <v>17</v>
@@ -5034,18 +5171,18 @@
         <v>24</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="17" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="D30" s="17" t="s">
         <v>17</v>
@@ -5057,18 +5194,18 @@
         <v>24</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="D31" s="17" t="s">
         <v>97</v>
@@ -5080,18 +5217,18 @@
         <v>24</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D32" s="17" t="s">
         <v>17</v>
@@ -5103,18 +5240,18 @@
         <v>24</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="D33" s="17" t="s">
         <v>17</v>
@@ -5126,18 +5263,18 @@
         <v>24</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="D34" s="17" t="s">
         <v>17</v>
@@ -5149,18 +5286,18 @@
         <v>24</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="D35" s="17" t="s">
         <v>17</v>
@@ -5172,18 +5309,18 @@
         <v>24</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="D36" s="17" t="s">
         <v>97</v>
@@ -5195,18 +5332,18 @@
         <v>24</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D37" s="17" t="s">
         <v>17</v>
@@ -5218,18 +5355,18 @@
         <v>24</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="D38" s="17" t="s">
         <v>17</v>
@@ -5241,18 +5378,18 @@
         <v>24</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="D39" s="17" t="s">
         <v>97</v>
@@ -5264,16 +5401,16 @@
         <v>24</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="7" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -5282,13 +5419,13 @@
     </row>
     <row r="41" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="D41" s="17" t="s">
         <v>48</v>
@@ -5300,18 +5437,18 @@
         <v>28</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="17" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="D42" s="17" t="s">
         <v>97</v>
@@ -5323,18 +5460,18 @@
         <v>28</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D43" s="17" t="s">
         <v>17</v>
@@ -5346,18 +5483,18 @@
         <v>28</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="17" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="D44" s="17" t="s">
         <v>17</v>
@@ -5369,18 +5506,18 @@
         <v>28</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="17" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="D45" s="17" t="s">
         <v>17</v>
@@ -5392,18 +5529,18 @@
         <v>28</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="17" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="D46" s="17" t="s">
         <v>97</v>
@@ -5415,16 +5552,16 @@
         <v>28</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="7" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
@@ -5433,13 +5570,13 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="17" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="D48" s="17" t="s">
         <v>48</v>
@@ -5451,18 +5588,18 @@
         <v>32</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="17" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="D49" s="17" t="s">
         <v>48</v>
@@ -5474,21 +5611,21 @@
         <v>32</v>
       </c>
       <c r="G49" s="15" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="E50" s="24" t="n">
         <v>103</v>
@@ -5497,18 +5634,18 @@
         <v>32</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="17" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="D51" s="17" t="s">
         <v>48</v>
@@ -5520,18 +5657,18 @@
         <v>32</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="17" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="D52" s="17" t="s">
         <v>17</v>
@@ -5543,21 +5680,21 @@
         <v>32</v>
       </c>
       <c r="G52" s="15" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="17" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="E53" s="24" t="n">
         <v>9</v>
@@ -5566,18 +5703,18 @@
         <v>32</v>
       </c>
       <c r="G53" s="15" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="17" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D54" s="17" t="s">
         <v>17</v>
@@ -5589,16 +5726,16 @@
         <v>32</v>
       </c>
       <c r="G54" s="15" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="7" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
@@ -5607,13 +5744,13 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="17" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="D56" s="17" t="s">
         <v>48</v>
@@ -5625,18 +5762,18 @@
         <v>37</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="17" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="D57" s="17" t="s">
         <v>17</v>
@@ -5648,18 +5785,18 @@
         <v>37</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="17" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D58" s="17" t="s">
         <v>17</v>
@@ -5671,18 +5808,18 @@
         <v>37</v>
       </c>
       <c r="G58" s="15" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="17" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="D59" s="17" t="s">
         <v>17</v>
@@ -5694,18 +5831,18 @@
         <v>37</v>
       </c>
       <c r="G59" s="15" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="17" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="D60" s="17" t="s">
         <v>17</v>
@@ -5717,18 +5854,18 @@
         <v>37</v>
       </c>
       <c r="G60" s="15" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="17" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="D61" s="17" t="s">
         <v>17</v>
@@ -5740,18 +5877,18 @@
         <v>37</v>
       </c>
       <c r="G61" s="15" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="17" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="D62" s="17" t="s">
         <v>17</v>
@@ -5763,18 +5900,18 @@
         <v>37</v>
       </c>
       <c r="G62" s="15" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="17" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="D63" s="17" t="s">
         <v>17</v>
@@ -5786,18 +5923,18 @@
         <v>37</v>
       </c>
       <c r="G63" s="15" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="17" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="D64" s="17" t="s">
         <v>97</v>
@@ -5809,18 +5946,18 @@
         <v>37</v>
       </c>
       <c r="G64" s="15" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="17" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="D65" s="17" t="s">
         <v>97</v>
@@ -5832,18 +5969,18 @@
         <v>37</v>
       </c>
       <c r="G65" s="15" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="17" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D66" s="17" t="s">
         <v>17</v>
@@ -5855,16 +5992,16 @@
         <v>37</v>
       </c>
       <c r="G66" s="15" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="7" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
@@ -5873,13 +6010,13 @@
     </row>
     <row r="68" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="17" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="D68" s="17" t="s">
         <v>17</v>
@@ -5891,87 +6028,87 @@
         <v>82</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="17" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>91</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>92</v>
+        <v>461</v>
       </c>
       <c r="D69" s="17" t="s">
         <v>48</v>
       </c>
       <c r="E69" s="24" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F69" s="38" t="s">
         <v>90</v>
       </c>
       <c r="G69" s="15" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="17" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="E70" s="24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F70" s="38" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="17" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D71" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E71" s="24" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="17" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D72" s="17" t="s">
         <v>17</v>
@@ -5982,17 +6119,19 @@
       <c r="F72" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="G72" s="15"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G72" s="15" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="17" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="D73" s="17" t="s">
         <v>17</v>
@@ -6001,407 +6140,453 @@
         <v>1</v>
       </c>
       <c r="F73" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="G73" s="15" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>94</v>
+      </c>
+      <c r="G73" s="15"/>
+    </row>
+    <row r="74" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="17" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="E74" s="24" t="n">
         <v>1</v>
       </c>
       <c r="F74" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G74" s="15" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="17" t="s">
+        <v>482</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E75" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="G74" s="15"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="17" t="s">
-        <v>473</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>475</v>
-      </c>
-      <c r="D75" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E75" s="24" t="n">
-        <v>55</v>
-      </c>
-      <c r="F75" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="G75" s="15" t="s">
-        <v>476</v>
-      </c>
+      <c r="G75" s="15"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="17" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="D76" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E76" s="24" t="n">
+        <v>55</v>
+      </c>
+      <c r="F76" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="G76" s="15" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="D77" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="E76" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="G76" s="15"/>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="B77" s="6"/>
-      <c r="C77" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="6"/>
-    </row>
-    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="17" t="s">
-        <v>482</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>484</v>
-      </c>
-      <c r="D78" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E78" s="24" t="n">
-        <v>245</v>
-      </c>
-      <c r="F78" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="G78" s="15" t="s">
-        <v>485</v>
-      </c>
+      <c r="E77" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="G77" s="15"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="B78" s="6"/>
+      <c r="C78" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
     </row>
     <row r="79" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="17" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="D79" s="17" t="s">
         <v>48</v>
       </c>
       <c r="E79" s="24" t="n">
-        <v>6</v>
+        <v>185</v>
       </c>
       <c r="F79" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="G79" s="15"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G79" s="15" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="17" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E80" s="24" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="F80" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="G80" s="15" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G80" s="15"/>
+    </row>
+    <row r="81" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="17" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E81" s="24" t="n">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="F81" s="38" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
       <c r="G81" s="15" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="17" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D82" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E82" s="24" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F82" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="G82" s="15"/>
+      <c r="G82" s="15" t="s">
+        <v>508</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="17" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="D83" s="17" t="s">
         <v>17</v>
       </c>
       <c r="E83" s="24" t="n">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="F83" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="G83" s="15"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="B84" s="6"/>
-      <c r="C84" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-    </row>
-    <row r="85" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G83" s="15" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="17" t="s">
+        <v>513</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="D84" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F84" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G84" s="15" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="17" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E85" s="24" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="F85" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="G85" s="15" t="s">
-        <v>508</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="G85" s="15"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="17" t="s">
-        <v>509</v>
-      </c>
-      <c r="B86" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D86" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E86" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="G86" s="15" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="B86" s="6"/>
+      <c r="C86" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6"/>
+    </row>
+    <row r="87" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="17" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="D87" s="17" t="s">
         <v>48</v>
       </c>
       <c r="E87" s="24" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="F87" s="38" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="17" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>516</v>
+        <v>117</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>517</v>
+        <v>118</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E88" s="24" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="F88" s="38" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="17" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="B89" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="D89" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E89" s="24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F89" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G89" s="15" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="17" t="s">
+        <v>532</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="D90" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E90" s="24" t="n">
+        <v>99</v>
+      </c>
+      <c r="F90" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="G90" s="15" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="17" t="s">
+        <v>536</v>
+      </c>
+      <c r="B91" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C89" s="10" t="s">
+      <c r="C91" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D89" s="17" t="s">
+      <c r="D91" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="E89" s="24" t="n">
+      <c r="E91" s="24" t="n">
         <v>63</v>
       </c>
-      <c r="F89" s="38" t="s">
+      <c r="F91" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="G89" s="15" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="B90" s="6"/>
-      <c r="C90" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="D90" s="6"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
-    </row>
-    <row r="91" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="17" t="s">
-        <v>523</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="C91" s="10" t="s">
-        <v>525</v>
-      </c>
-      <c r="D91" s="17" t="s">
+      <c r="G91" s="15" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="B92" s="6"/>
+      <c r="C92" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6"/>
+    </row>
+    <row r="93" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="17" t="s">
+        <v>540</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>542</v>
+      </c>
+      <c r="D93" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E91" s="24" t="n">
+      <c r="E93" s="24" t="n">
         <v>518</v>
       </c>
-      <c r="F91" s="38" t="s">
+      <c r="F93" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="G91" s="15" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="17" t="s">
-        <v>527</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="D92" s="17" t="s">
+      <c r="G93" s="15" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="D94" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E92" s="24" t="n">
+      <c r="E94" s="24" t="n">
         <v>166</v>
       </c>
-      <c r="F92" s="38" t="s">
+      <c r="F94" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="G92" s="15" t="s">
-        <v>530</v>
+      <c r="G94" s="15" t="s">
+        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -6437,17 +6622,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>533</v>
+        <v>550</v>
       </c>
       <c r="B4" s="39" t="n">
         <v>49.5</v>
@@ -6455,7 +6640,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>534</v>
+        <v>551</v>
       </c>
       <c r="B5" s="39" t="n">
         <v>-0.25</v>
@@ -6463,7 +6648,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="B6" s="39" t="n">
         <v>-30</v>
@@ -6471,7 +6656,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="B7" s="39" t="n">
         <v>37</v>
@@ -6479,7 +6664,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="B8" s="39" t="n">
         <v>45.93</v>
@@ -6487,7 +6672,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>538</v>
+        <v>555</v>
       </c>
       <c r="B9" s="39" t="n">
         <v>17.51</v>
@@ -6495,7 +6680,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>539</v>
+        <v>556</v>
       </c>
       <c r="B10" s="39" t="n">
         <v>18.51</v>
@@ -6503,7 +6688,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="B11" s="39" t="n">
         <v>1000</v>
@@ -6511,7 +6696,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="B12" s="39" t="n">
         <v>200</v>
@@ -6519,7 +6704,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="B13" s="39" t="n">
         <v>850</v>
@@ -6527,7 +6712,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="B14" s="39" t="n">
         <v>250</v>
@@ -6535,7 +6720,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>544</v>
+        <v>561</v>
       </c>
       <c r="B15" s="39" t="n">
         <v>40</v>
@@ -6543,7 +6728,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>545</v>
+        <v>562</v>
       </c>
       <c r="B16" s="39" t="n">
         <v>60</v>
@@ -6551,45 +6736,45 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>552</v>
+        <v>569</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">Параметри!B13</f>
@@ -6638,45 +6823,45 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>569</v>
+        <v>586</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>1</v>
@@ -6685,10 +6870,10 @@
         <v>12</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="F22" s="39" t="n">
         <v>3.1</v>
@@ -6714,7 +6899,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>1</v>
@@ -6723,10 +6908,10 @@
         <v>12</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="F23" s="39" t="n">
         <v>9</v>
@@ -6752,7 +6937,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>2</v>
@@ -6761,10 +6946,10 @@
         <v>12</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="F24" s="39" t="n">
         <v>10.9</v>
@@ -6790,7 +6975,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>2</v>
@@ -6799,10 +6984,10 @@
         <v>12</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="F25" s="39" t="n">
         <v>14</v>
@@ -6828,7 +7013,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>3</v>
@@ -6837,10 +7022,10 @@
         <v>12</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F26" s="39" t="n">
         <v>3.1</v>
@@ -6866,7 +7051,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>3</v>
@@ -6875,10 +7060,10 @@
         <v>12</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F27" s="39" t="n">
         <v>4</v>
@@ -6904,7 +7089,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>4</v>
@@ -6913,10 +7098,10 @@
         <v>12</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F28" s="39" t="n">
         <v>11.4</v>
@@ -6942,7 +7127,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="B29" s="8" t="n">
         <v>4</v>
@@ -6951,10 +7136,10 @@
         <v>12</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F29" s="39" t="n">
         <v>7.7</v>
@@ -6980,7 +7165,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
       <c r="B30" s="8" t="n">
         <v>5</v>
@@ -6989,10 +7174,10 @@
         <v>12</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F30" s="39" t="n">
         <v>15</v>
@@ -7018,7 +7203,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="B31" s="8" t="n">
         <v>5</v>
@@ -7027,10 +7212,10 @@
         <v>12</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="F31" s="39" t="n">
         <v>15</v>
@@ -7056,7 +7241,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="B32" s="8" t="n">
         <v>6</v>
@@ -7065,10 +7250,10 @@
         <v>12</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="F32" s="39" t="n">
         <v>71.2</v>
@@ -7094,7 +7279,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>588</v>
+        <v>605</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="n">
@@ -7128,7 +7313,7 @@
     </row>
     <row r="35" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="36" t="s">
-        <v>589</v>
+        <v>606</v>
       </c>
       <c r="B35" s="36"/>
       <c r="C35" s="36"/>
@@ -7161,7 +7346,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="70"/>
@@ -7172,107 +7357,107 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>592</v>
+        <v>609</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>593</v>
+        <v>610</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="B5" s="24" t="n">
         <v>86</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>597</v>
+        <v>614</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
       <c r="B6" s="24" t="n">
         <v>31</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>599</v>
+        <v>616</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="B7" s="24" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>601</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>602</v>
+        <v>619</v>
       </c>
       <c r="B8" s="24" t="n">
         <v>9</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>601</v>
+        <v>618</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>603</v>
+        <v>620</v>
       </c>
       <c r="B9" s="21" t="n">
         <f aca="false">B5+B6+B7+B8</f>
         <v>132</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>604</v>
+        <v>621</v>
       </c>
       <c r="B10" s="21" t="n">
-        <f aca="false">ROUNDUP(B9*$B$30,0)</f>
+        <f aca="false">ROUNDUP(B9*$B$31,0)</f>
         <v>135</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>73</v>
@@ -7280,775 +7465,859 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>605</v>
+        <v>622</v>
       </c>
       <c r="B11" s="31" t="n">
-        <f aca="false">B9*$B$28/1000</f>
+        <f aca="false">B9*$B$29/1000</f>
         <v>96.36</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>606</v>
+        <v>623</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>607</v>
+        <v>624</v>
       </c>
       <c r="B12" s="24" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>608</v>
+        <v>625</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="B13" s="24" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>610</v>
+        <v>627</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>611</v>
+        <v>628</v>
       </c>
       <c r="B14" s="45" t="n">
         <v>87.1</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>612</v>
+        <v>629</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>613</v>
+        <v>630</v>
       </c>
       <c r="B15" s="24" t="n">
         <v>65</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>614</v>
+        <v>631</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>615</v>
+        <v>632</v>
       </c>
       <c r="B16" s="21" t="n">
-        <f aca="false">ROUNDUP(($B$45+B15)*1.01,0)</f>
+        <f aca="false">ROUNDUP(($B$46+B15)*1.01,0)</f>
         <v>684</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
       <c r="B17" s="24" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>454</v>
+        <v>636</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>619</v>
+        <v>637</v>
       </c>
       <c r="B18" s="24" t="n">
         <v>55</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="B19" s="24" t="n">
         <v>5.8</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>508</v>
+        <v>525</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>621</v>
+        <v>639</v>
       </c>
       <c r="B20" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>510</v>
+        <v>527</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="B21" s="24" t="n">
         <v>5.6</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>623</v>
+        <v>641</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>624</v>
+        <v>642</v>
       </c>
       <c r="B22" s="24" t="n">
         <v>99</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="B23" s="24" t="n">
         <v>63</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>626</v>
+        <v>644</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>627</v>
+        <v>645</v>
       </c>
       <c r="B24" s="24" t="n">
         <v>112</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>628</v>
+        <v>646</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="B25" s="24" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>630</v>
+        <v>648</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="46"/>
-      <c r="D26" s="46"/>
-    </row>
-    <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="47" t="s">
-        <v>631</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="C27" s="4" t="s">
+      <c r="A26" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>31</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="46"/>
+      <c r="D27" s="46"/>
+    </row>
+    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="47" t="s">
+        <v>651</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="47" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="B28" s="24" t="n">
-        <v>730</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>633</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>634</v>
+      <c r="D28" s="47" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>635</v>
-      </c>
-      <c r="B29" s="48" t="n">
-        <v>44.89</v>
+        <v>652</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>730</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>636</v>
+        <v>653</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>637</v>
+        <v>654</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="B30" s="49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="C30" s="8"/>
+        <v>655</v>
+      </c>
+      <c r="B30" s="48" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>656</v>
+      </c>
       <c r="D30" s="15" t="s">
-        <v>73</v>
+        <v>657</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>639</v>
-      </c>
-      <c r="B31" s="50" t="n">
+        <v>658</v>
+      </c>
+      <c r="B31" s="49" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="15" t="s">
         <v>73</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="B32" s="51" t="n">
+        <v>659</v>
+      </c>
+      <c r="B32" s="50" t="n">
+        <v>73</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="B33" s="51" t="n">
         <f aca="false">21500/1925</f>
         <v>11.1688311688312</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="s">
-        <v>645</v>
-      </c>
-      <c r="B33" s="51" t="n">
+      <c r="C33" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="B34" s="51" t="n">
         <f aca="false">11211/1260+4*0.5</f>
         <v>10.897619047619</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
-        <v>647</v>
-      </c>
-      <c r="B34" s="51" t="n">
+      <c r="C34" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="B35" s="51" t="n">
         <f aca="false">2555/297</f>
         <v>8.6026936026936</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="D34" s="15" t="s">
+      <c r="C35" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="D35" s="15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="B35" s="51" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="B36" s="51" t="n">
         <f aca="false">11520/192</f>
         <v>60</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>649</v>
-      </c>
-      <c r="D35" s="15" t="s">
+      <c r="C36" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="D36" s="15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="B36" s="51" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="B37" s="51" t="n">
         <f aca="false">12398/192</f>
         <v>64.5729166666667</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>649</v>
-      </c>
-      <c r="D36" s="15" t="s">
+      <c r="C37" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="D37" s="15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="s">
-        <v>651</v>
-      </c>
-      <c r="B37" s="51" t="n">
+    <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="B38" s="51" t="n">
         <f aca="false">2400/2112</f>
         <v>1.13636363636364</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="D37" s="15" t="s">
+      <c r="C38" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9" t="s">
-        <v>652</v>
-      </c>
-      <c r="B38" s="34" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="B39" s="34" t="n">
         <f aca="false">276/1050</f>
         <v>0.262857142857143</v>
       </c>
-      <c r="C38" s="8" t="s">
-        <v>653</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9" t="s">
-        <v>655</v>
-      </c>
-      <c r="B39" s="52" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C39" s="8"/>
+      <c r="C39" s="8" t="s">
+        <v>673</v>
+      </c>
       <c r="D39" s="15" t="s">
-        <v>656</v>
+        <v>674</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="B40" s="51" t="n">
+        <v>675</v>
+      </c>
+      <c r="B40" s="52" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="15" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="B41" s="51" t="n">
         <f aca="false">7000/594</f>
         <v>11.7845117845118</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="D40" s="15" t="s">
+      <c r="C41" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="D41" s="15" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="B41" s="51" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="B42" s="51" t="n">
         <f aca="false">14000/2112</f>
         <v>6.62878787878788</v>
       </c>
-      <c r="C41" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="D41" s="15" t="s">
+      <c r="C42" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="D42" s="15" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9" t="s">
-        <v>659</v>
-      </c>
-      <c r="B42" s="52" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="15" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>660</v>
-      </c>
-      <c r="B43" s="34" t="n">
+        <v>679</v>
+      </c>
+      <c r="B43" s="52" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="C43" s="8"/>
+      <c r="D43" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="B44" s="34" t="n">
         <f aca="false">4840.7596950824/4234.64192</f>
         <v>1.14313318257672</v>
       </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="15" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9" t="s">
-        <v>662</v>
-      </c>
-      <c r="B44" s="50" t="n">
+      <c r="C44" s="8"/>
+      <c r="D44" s="15" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="B45" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="C44" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="B45" s="53" t="n">
+      <c r="C45" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="B46" s="53" t="n">
         <v>612</v>
       </c>
-      <c r="C45" s="8" t="s">
-        <v>596</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9" t="s">
-        <v>666</v>
-      </c>
-      <c r="B46" s="53" t="n">
-        <v>164</v>
-      </c>
       <c r="C46" s="8" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="B47" s="34" t="n">
+        <v>686</v>
+      </c>
+      <c r="B47" s="53" t="n">
+        <v>164</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="B48" s="34" t="n">
         <f aca="false">2107/6227</f>
         <v>0.338365183876666</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="D47" s="15" t="s">
+      <c r="C48" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="D48" s="15" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="B48" s="50" t="n">
-        <v>50</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>670</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
-        <v>671</v>
-      </c>
-      <c r="B49" s="51" t="n">
+        <v>689</v>
+      </c>
+      <c r="B49" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="B50" s="51" t="n">
         <f aca="false">3080/2112</f>
         <v>1.45833333333333</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="D49" s="15" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="s">
-        <v>672</v>
-      </c>
-      <c r="B50" s="51" t="n">
+      <c r="C50" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="B51" s="51" t="n">
         <f aca="false">2584/2112</f>
         <v>1.22348484848485</v>
       </c>
-      <c r="C50" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="B51" s="42" t="n">
-        <v>700</v>
-      </c>
       <c r="C51" s="8" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>675</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
-        <v>676</v>
-      </c>
-      <c r="B52" s="52" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C52" s="8"/>
+        <v>693</v>
+      </c>
+      <c r="B52" s="42" t="n">
+        <v>700</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>694</v>
+      </c>
       <c r="D52" s="15" t="s">
-        <v>166</v>
+        <v>695</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
-        <v>677</v>
+        <v>696</v>
       </c>
       <c r="B53" s="52" t="n">
-        <v>0.18</v>
+        <v>0.04</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="15" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
-        <v>678</v>
+        <v>697</v>
       </c>
       <c r="B54" s="52" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="15" t="s">
-        <v>679</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
-        <v>680</v>
-      </c>
-      <c r="B55" s="48" t="n">
-        <v>7</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>681</v>
-      </c>
+        <v>698</v>
+      </c>
+      <c r="B55" s="52" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C55" s="8"/>
       <c r="D55" s="15" t="s">
-        <v>682</v>
+        <v>699</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="B56" s="52" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="C56" s="8"/>
+        <v>700</v>
+      </c>
+      <c r="B56" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>701</v>
+      </c>
       <c r="D56" s="15" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
-        <v>685</v>
-      </c>
-      <c r="B57" s="50" t="n">
-        <v>44.99</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>640</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="B57" s="52" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="C57" s="8"/>
       <c r="D57" s="15" t="s">
-        <v>686</v>
+        <v>704</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9" t="s">
-        <v>687</v>
-      </c>
-      <c r="B58" s="48" t="n">
-        <v>139829</v>
+        <v>705</v>
+      </c>
+      <c r="B58" s="50" t="n">
+        <v>3.17</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>688</v>
+        <v>673</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>85</v>
+        <v>706</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9" t="s">
-        <v>689</v>
-      </c>
-      <c r="B59" s="48" t="n">
-        <v>3224.24</v>
+        <v>707</v>
+      </c>
+      <c r="B59" s="50" t="n">
+        <v>44.99</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>688</v>
+        <v>660</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>93</v>
+        <v>708</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
-        <v>690</v>
+        <v>709</v>
       </c>
       <c r="B60" s="48" t="n">
-        <v>11237</v>
+        <v>139829</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>688</v>
+        <v>710</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>691</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="9" t="s">
-        <v>692</v>
+        <v>711</v>
       </c>
       <c r="B61" s="48" t="n">
-        <v>4741.82</v>
+        <v>3224.24</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>688</v>
+        <v>710</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>693</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="B62" s="48" t="n">
-        <v>7096</v>
+        <v>11237</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>688</v>
+        <v>710</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>106</v>
+        <v>713</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="s">
-        <v>695</v>
+        <v>714</v>
       </c>
       <c r="B63" s="48" t="n">
-        <v>9000</v>
+        <v>4741.82</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>688</v>
+        <v>710</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>115</v>
+        <v>715</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
       <c r="B64" s="48" t="n">
-        <v>717.75</v>
+        <v>7096</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>688</v>
+        <v>710</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="9" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="B65" s="48" t="n">
-        <v>1090</v>
+        <v>9000</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>688</v>
+        <v>710</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="9" t="s">
-        <v>698</v>
+        <v>718</v>
       </c>
       <c r="B66" s="48" t="n">
+        <v>717.75</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="B67" s="48" t="n">
+        <v>1090</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="B68" s="48" t="n">
         <v>6672.64</v>
       </c>
-      <c r="C66" s="8" t="s">
-        <v>688</v>
-      </c>
-      <c r="D66" s="15" t="s">
+      <c r="C68" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="D68" s="15" t="s">
         <v>102</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="B69" s="48" t="n">
+        <v>273.73</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="B70" s="48" t="n">
+        <v>385</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="B71" s="48" t="n">
+        <v>171.86</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="B72" s="48" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
